--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77A4AD6-A68E-4336-B0B7-1B15AB91FF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEC7A83-CC73-48D2-ADB1-CFDA5B26FB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -2980,7 +2980,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6">
-        <v>3067</v>
+        <v>2867</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -3779,7 +3779,7 @@
         <v>436</v>
       </c>
       <c r="C56" s="4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D56" s="3">
         <v>5</v>
@@ -3966,7 +3966,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="6">
-        <v>513</v>
+        <v>413</v>
       </c>
       <c r="D67" s="5">
         <v>5</v>
@@ -4187,7 +4187,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D80" s="3">
         <v>4</v>
@@ -4323,7 +4323,7 @@
         <v>474</v>
       </c>
       <c r="C88" s="4">
-        <v>635</v>
+        <v>435</v>
       </c>
       <c r="D88" s="3">
         <v>2</v>
@@ -5547,7 +5547,7 @@
         <v>134</v>
       </c>
       <c r="C160" s="4">
-        <v>1676</v>
+        <v>1476</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -6057,7 +6057,7 @@
         <v>164</v>
       </c>
       <c r="C190" s="4">
-        <v>3100</v>
+        <v>2800</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6159,7 +6159,7 @@
         <v>172</v>
       </c>
       <c r="C196" s="4">
-        <v>2318</v>
+        <v>2118</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6601,7 +6601,7 @@
         <v>628</v>
       </c>
       <c r="C222" s="4">
-        <v>638</v>
+        <v>138</v>
       </c>
       <c r="D222" s="3">
         <v>4</v>
@@ -6975,7 +6975,7 @@
         <v>212</v>
       </c>
       <c r="C244" s="4">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="D244" s="3">
         <v>5</v>
@@ -7145,7 +7145,7 @@
         <v>222</v>
       </c>
       <c r="C254" s="4">
-        <v>601</v>
+        <v>401</v>
       </c>
       <c r="D254" s="3">
         <v>2</v>
@@ -7825,7 +7825,7 @@
         <v>262</v>
       </c>
       <c r="C294" s="4">
-        <v>2419</v>
+        <v>1735</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -8131,7 +8131,7 @@
         <v>286</v>
       </c>
       <c r="C312" s="4">
-        <v>1607</v>
+        <v>987</v>
       </c>
       <c r="D312" s="3">
         <v>5</v>
@@ -8250,7 +8250,7 @@
         <v>296</v>
       </c>
       <c r="C319" s="6">
-        <v>1315</v>
+        <v>786</v>
       </c>
       <c r="D319" s="5">
         <v>5</v>
@@ -8369,7 +8369,7 @@
         <v>732</v>
       </c>
       <c r="C326" s="4">
-        <v>675</v>
+        <v>190</v>
       </c>
       <c r="D326" s="3">
         <v>4</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEC7A83-CC73-48D2-ADB1-CFDA5B26FB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5CAE23-9E11-4EC3-939A-EE97C422BC25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3235,7 +3235,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="4">
-        <v>1290</v>
+        <v>1190</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -3490,7 +3490,7 @@
         <v>414</v>
       </c>
       <c r="C39" s="6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="D39" s="5">
         <v>3</v>
@@ -5717,7 +5717,7 @@
         <v>578</v>
       </c>
       <c r="C170" s="4">
-        <v>1000</v>
+        <v>855</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>777</v>
@@ -6091,7 +6091,7 @@
         <v>600</v>
       </c>
       <c r="C192" s="4">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="D192" s="3">
         <v>3</v>
@@ -7281,7 +7281,7 @@
         <v>232</v>
       </c>
       <c r="C262" s="4">
-        <v>1279</v>
+        <v>1079</v>
       </c>
       <c r="D262" s="3">
         <v>6</v>
@@ -7604,7 +7604,7 @@
         <v>252</v>
       </c>
       <c r="C281" s="6">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -8216,7 +8216,7 @@
         <v>292</v>
       </c>
       <c r="C317" s="6">
-        <v>1302</v>
+        <v>1152</v>
       </c>
       <c r="D317" s="5">
         <v>6</v>
@@ -8250,7 +8250,7 @@
         <v>296</v>
       </c>
       <c r="C319" s="6">
-        <v>786</v>
+        <v>686</v>
       </c>
       <c r="D319" s="5">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5CAE23-9E11-4EC3-939A-EE97C422BC25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A255759-C31D-4E69-8245-C434A20F4D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="787">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -298,9 +298,6 @@
     <t>0099-W</t>
   </si>
   <si>
-    <t xml:space="preserve">بوا امبريال اسينشيال - للجنسين </t>
-  </si>
-  <si>
     <t>0100-U</t>
   </si>
   <si>
@@ -2384,6 +2381,21 @@
   </si>
   <si>
     <t>3ط2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بوا امبريال اسينتيال - للجنسين </t>
+  </si>
+  <si>
+    <t>هيرش لهب العز للعود - للجنسين</t>
+  </si>
+  <si>
+    <t>0387-U</t>
+  </si>
+  <si>
+    <t>سيمفوني من لويس فيتون - للجنسين</t>
+  </si>
+  <si>
+    <t>0388-U</t>
   </si>
 </sst>
 </file>
@@ -2826,7 +2838,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E387"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.26953125" bestFit="1" customWidth="1"/>
@@ -2855,53 +2867,53 @@
     </row>
     <row r="2" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>380</v>
-      </c>
       <c r="C2" s="4">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>382</v>
-      </c>
       <c r="C3" s="6">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>384</v>
-      </c>
       <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2923,53 +2935,53 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>388</v>
-      </c>
       <c r="C7" s="6">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>390</v>
-      </c>
       <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3008,19 +3020,19 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>392</v>
-      </c>
       <c r="C11" s="6">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -3042,19 +3054,19 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>394</v>
-      </c>
       <c r="C13" s="6">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -3093,36 +3105,36 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>396</v>
-      </c>
       <c r="C16" s="4">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>398</v>
-      </c>
       <c r="C17" s="6">
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -3161,27 +3173,27 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="C20" s="4">
         <v>0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>401</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>402</v>
       </c>
       <c r="C21" s="6">
         <v>0</v>
@@ -3190,24 +3202,24 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="C22" s="4">
         <v>0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -3221,10 +3233,10 @@
         <v>5069</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -3280,19 +3292,19 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>406</v>
-      </c>
       <c r="C27" s="6">
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -3326,24 +3338,24 @@
         <v>3</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="C30" s="4">
         <v>0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -3399,19 +3411,19 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>410</v>
-      </c>
       <c r="C34" s="4">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -3467,27 +3479,27 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>412</v>
-      </c>
       <c r="C38" s="4">
         <v>0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>413</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>414</v>
       </c>
       <c r="C39" s="6">
         <v>900</v>
@@ -3501,36 +3513,36 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="C40" s="4">
         <v>0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>418</v>
-      </c>
       <c r="C41" s="6">
         <v>0</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -3569,19 +3581,19 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>420</v>
-      </c>
       <c r="C44" s="4">
         <v>0</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -3603,19 +3615,19 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="C46" s="4">
         <v>0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -3637,36 +3649,36 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>424</v>
-      </c>
       <c r="C48" s="4">
         <v>0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>426</v>
-      </c>
       <c r="C49" s="6">
         <v>0</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -3683,7 +3695,7 @@
         <v>3</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -3705,78 +3717,78 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>428</v>
-      </c>
       <c r="C52" s="4">
         <v>0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>430</v>
-      </c>
       <c r="C53" s="6">
         <v>0</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>432</v>
-      </c>
       <c r="C54" s="4">
         <v>0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>434</v>
-      </c>
       <c r="C55" s="6">
         <v>0</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="C56" s="4">
         <v>500</v>
@@ -3790,36 +3802,36 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>438</v>
-      </c>
       <c r="C57" s="6">
         <v>0</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>440</v>
-      </c>
       <c r="C58" s="4">
         <v>0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
@@ -3841,36 +3853,36 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="C60" s="4">
         <v>0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>444</v>
-      </c>
       <c r="C61" s="6">
         <v>0</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -3892,19 +3904,19 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>446</v>
-      </c>
       <c r="C63" s="6">
         <v>0</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -3926,19 +3938,19 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>448</v>
-      </c>
       <c r="C65" s="6">
         <v>0</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -3955,7 +3967,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -3977,61 +3989,61 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>450</v>
-      </c>
       <c r="C68" s="4">
         <v>0</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>452</v>
-      </c>
       <c r="C69" s="6">
         <v>0</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="C70" s="4">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>456</v>
       </c>
       <c r="C71" s="6">
         <v>847</v>
@@ -4040,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -4062,36 +4074,36 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>458</v>
       </c>
       <c r="C73" s="6">
         <v>1000</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>460</v>
-      </c>
       <c r="C74" s="4">
         <v>0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -4113,53 +4125,53 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="C76" s="4">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>464</v>
-      </c>
       <c r="C77" s="6">
         <v>0</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>466</v>
-      </c>
       <c r="C78" s="4">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -4198,53 +4210,53 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="C81" s="6">
         <v>0</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="C82" s="4">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="B83" s="5" t="s">
-        <v>472</v>
-      </c>
       <c r="C83" s="6">
         <v>0</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
@@ -4312,15 +4324,15 @@
         <v>3</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="C88" s="4">
         <v>435</v>
@@ -4334,53 +4346,53 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>476</v>
-      </c>
       <c r="C89" s="6">
         <v>0</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>478</v>
-      </c>
       <c r="C90" s="4">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>480</v>
-      </c>
       <c r="C91" s="6">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
@@ -4402,95 +4414,95 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>482</v>
-      </c>
       <c r="C93" s="6">
         <v>0</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="C94" s="4">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B95" s="5" t="s">
-        <v>486</v>
-      </c>
       <c r="C95" s="6">
         <v>0</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>488</v>
-      </c>
       <c r="C96" s="4">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="B97" s="5" t="s">
-        <v>490</v>
-      </c>
       <c r="C97" s="6">
         <v>0</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="C98" s="4">
         <v>1000</v>
@@ -4504,19 +4516,19 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="B99" s="5" t="s">
-        <v>494</v>
-      </c>
       <c r="C99" s="6">
         <v>0</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
@@ -4538,61 +4550,61 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B101" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="C101" s="6">
-        <v>564</v>
-      </c>
-      <c r="D101" s="5">
-        <v>3</v>
-      </c>
-      <c r="E101" s="5">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="C102" s="4">
         <v>0</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B103" s="5" t="s">
-        <v>498</v>
-      </c>
       <c r="C103" s="6">
         <v>0</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C104" s="4">
         <v>601</v>
@@ -4606,10 +4618,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="C105" s="6">
         <v>251</v>
@@ -4623,95 +4635,95 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="C106" s="4">
         <v>0</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B107" s="5" t="s">
-        <v>502</v>
-      </c>
       <c r="C107" s="6">
         <v>0</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>504</v>
-      </c>
       <c r="C108" s="4">
         <v>0</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B109" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="B109" s="5" t="s">
-        <v>506</v>
-      </c>
       <c r="C109" s="6">
         <v>0</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>508</v>
-      </c>
       <c r="C110" s="4">
         <v>0</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="C111" s="6">
         <v>0</v>
@@ -4725,10 +4737,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="C112" s="4">
         <v>2003</v>
@@ -4742,61 +4754,61 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B113" s="5" t="s">
-        <v>510</v>
-      </c>
       <c r="C113" s="6">
         <v>0</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>512</v>
-      </c>
       <c r="C114" s="4">
         <v>0</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>514</v>
-      </c>
       <c r="C115" s="6">
         <v>0</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="C116" s="4">
         <v>1000</v>
@@ -4810,10 +4822,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="C117" s="6">
         <v>266</v>
@@ -4827,27 +4839,27 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>518</v>
-      </c>
       <c r="C118" s="4">
         <v>0</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="C119" s="6">
         <v>948</v>
@@ -4861,10 +4873,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="C120" s="4">
         <v>559</v>
@@ -4878,27 +4890,27 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B121" s="5" t="s">
-        <v>520</v>
-      </c>
       <c r="C121" s="6">
         <v>0</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C122" s="4">
         <v>1000</v>
@@ -4912,10 +4924,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="C123" s="6">
         <v>542</v>
@@ -4929,61 +4941,61 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="C124" s="4">
         <v>550</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="B125" s="5" t="s">
-        <v>524</v>
-      </c>
       <c r="C125" s="6">
         <v>0</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B126" s="3" t="s">
-        <v>526</v>
-      </c>
       <c r="C126" s="4">
         <v>0</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="C127" s="6">
         <v>451</v>
@@ -4997,44 +5009,44 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B128" s="3" t="s">
-        <v>528</v>
-      </c>
       <c r="C128" s="4">
         <v>0</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="C129" s="6">
         <v>50</v>
       </c>
       <c r="D129" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E129" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="C130" s="4">
         <v>608</v>
@@ -5048,27 +5060,27 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B131" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="B131" s="5" t="s">
-        <v>530</v>
-      </c>
       <c r="C131" s="6">
         <v>0</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="C132" s="4">
         <v>979</v>
@@ -5082,27 +5094,27 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="B133" s="5" t="s">
-        <v>532</v>
-      </c>
       <c r="C133" s="6">
         <v>0</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B134" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>534</v>
       </c>
       <c r="C134" s="4">
         <v>776</v>
@@ -5116,78 +5128,78 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="B135" s="5" t="s">
-        <v>536</v>
-      </c>
       <c r="C135" s="6">
         <v>0</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B136" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>538</v>
-      </c>
       <c r="C136" s="4">
         <v>0</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B137" s="5" t="s">
-        <v>540</v>
-      </c>
       <c r="C137" s="6">
         <v>0</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B138" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>542</v>
-      </c>
       <c r="C138" s="4">
         <v>0</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="C139" s="6">
         <v>743</v>
@@ -5201,10 +5213,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B140" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="C140" s="4">
         <v>609</v>
@@ -5218,27 +5230,27 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="B141" s="5" t="s">
-        <v>544</v>
-      </c>
       <c r="C141" s="6">
         <v>0</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B142" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="C142" s="4">
         <v>1218</v>
@@ -5247,15 +5259,15 @@
         <v>2</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="C143" s="6">
         <v>1000</v>
@@ -5269,27 +5281,27 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B144" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>546</v>
-      </c>
       <c r="C144" s="4">
         <v>0</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C145" s="6">
         <v>701</v>
@@ -5303,44 +5315,44 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="B146" s="3" t="s">
-        <v>548</v>
-      </c>
       <c r="C146" s="4">
         <v>0</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="B147" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="B147" s="5" t="s">
-        <v>550</v>
-      </c>
       <c r="C147" s="6">
         <v>0</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C148" s="4">
         <v>1000</v>
@@ -5354,95 +5366,95 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="B149" s="5" t="s">
-        <v>552</v>
-      </c>
       <c r="C149" s="6">
         <v>0</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="B150" s="3" t="s">
-        <v>554</v>
-      </c>
       <c r="C150" s="4">
         <v>0</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="B151" s="5" t="s">
-        <v>556</v>
-      </c>
       <c r="C151" s="6">
         <v>0</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="B152" s="3" t="s">
-        <v>558</v>
-      </c>
       <c r="C152" s="4">
         <v>0</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="B153" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="B153" s="5" t="s">
-        <v>560</v>
-      </c>
       <c r="C153" s="6">
         <v>0</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B154" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="C154" s="4">
         <v>0</v>
@@ -5456,10 +5468,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="C155" s="6">
         <v>0</v>
@@ -5473,44 +5485,44 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B156" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="B156" s="3" t="s">
-        <v>562</v>
-      </c>
       <c r="C156" s="4">
         <v>0</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="B157" s="5" t="s">
-        <v>564</v>
-      </c>
       <c r="C157" s="6">
         <v>0</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B158" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="C158" s="4">
         <v>0</v>
@@ -5524,27 +5536,27 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="B159" s="5" t="s">
-        <v>566</v>
-      </c>
       <c r="C159" s="6">
         <v>0</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B160" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="C160" s="4">
         <v>1476</v>
@@ -5558,10 +5570,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="C161" s="6">
         <v>196</v>
@@ -5575,44 +5587,44 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B162" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B162" s="3" t="s">
-        <v>568</v>
-      </c>
       <c r="C162" s="4">
         <v>0</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="B163" s="5" t="s">
-        <v>570</v>
-      </c>
       <c r="C163" s="6">
         <v>0</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B164" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="C164" s="4">
         <v>2757</v>
@@ -5626,44 +5638,44 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="B165" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="B165" s="5" t="s">
-        <v>572</v>
-      </c>
       <c r="C165" s="6">
         <v>0</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B166" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>574</v>
-      </c>
       <c r="C166" s="4">
         <v>0</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="C167" s="6">
         <v>603</v>
@@ -5677,10 +5689,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B168" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="C168" s="4">
         <v>316</v>
@@ -5694,61 +5706,61 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="B169" s="5" t="s">
-        <v>576</v>
-      </c>
       <c r="C169" s="6">
         <v>0</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B170" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>578</v>
       </c>
       <c r="C170" s="4">
         <v>855</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B171" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="C171" s="6">
         <v>2306</v>
       </c>
       <c r="D171" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B172" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C172" s="4">
         <v>739</v>
@@ -5762,10 +5774,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B173" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="C173" s="6">
         <v>0</v>
@@ -5779,27 +5791,27 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B174" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B174" s="3" t="s">
-        <v>580</v>
-      </c>
       <c r="C174" s="4">
         <v>0</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="C175" s="6">
         <v>1008</v>
@@ -5813,10 +5825,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B176" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="C176" s="4">
         <v>700</v>
@@ -5830,95 +5842,95 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="B177" s="5" t="s">
-        <v>582</v>
-      </c>
       <c r="C177" s="6">
         <v>0</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B178" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B178" s="3" t="s">
-        <v>584</v>
-      </c>
       <c r="C178" s="4">
         <v>0</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="B179" s="5" t="s">
-        <v>586</v>
-      </c>
       <c r="C179" s="6">
         <v>0</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B180" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B180" s="3" t="s">
-        <v>588</v>
-      </c>
       <c r="C180" s="4">
         <v>0</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="C181" s="6">
         <v>286</v>
       </c>
       <c r="D181" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E181" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B182" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="C182" s="4">
         <v>307</v>
@@ -5932,95 +5944,95 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="B183" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="B183" s="5" t="s">
-        <v>590</v>
-      </c>
       <c r="C183" s="6">
         <v>0</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="B184" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B184" s="3" t="s">
-        <v>592</v>
-      </c>
       <c r="C184" s="4">
         <v>0</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="B185" s="5" t="s">
-        <v>594</v>
-      </c>
       <c r="C185" s="6">
         <v>0</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B186" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="C186" s="4">
         <v>110</v>
       </c>
       <c r="D186" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E186" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="E186" s="3" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="C187" s="6">
         <v>10</v>
       </c>
       <c r="D187" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E187" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B188" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B188" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="C188" s="4">
         <v>868</v>
@@ -6029,35 +6041,35 @@
         <v>3</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="B189" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B189" s="5" t="s">
-        <v>596</v>
-      </c>
       <c r="C189" s="6">
         <v>0</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B190" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B190" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="C190" s="4">
-        <v>2800</v>
+        <v>2300</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6068,27 +6080,27 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="B191" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="B191" s="5" t="s">
-        <v>598</v>
-      </c>
       <c r="C191" s="6">
         <v>0</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B192" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="B192" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="C192" s="4">
         <v>1000</v>
@@ -6102,10 +6114,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B193" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="C193" s="6">
         <v>707</v>
@@ -6119,10 +6131,10 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B194" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="C194" s="4">
         <v>120</v>
@@ -6136,10 +6148,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B195" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B195" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="C195" s="6">
         <v>9</v>
@@ -6153,10 +6165,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B196" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="C196" s="4">
         <v>2118</v>
@@ -6170,44 +6182,44 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="B197" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="B197" s="5" t="s">
-        <v>602</v>
-      </c>
       <c r="C197" s="6">
         <v>0</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B198" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="B198" s="3" t="s">
-        <v>604</v>
-      </c>
       <c r="C198" s="4">
         <v>0</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B199" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="C199" s="6">
         <v>235</v>
@@ -6221,27 +6233,27 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B200" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="B200" s="3" t="s">
-        <v>606</v>
-      </c>
       <c r="C200" s="4">
         <v>0</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B201" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="C201" s="6">
         <v>1202</v>
@@ -6255,10 +6267,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B202" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="C202" s="4">
         <v>215</v>
@@ -6272,10 +6284,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B203" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="C203" s="6">
         <v>205</v>
@@ -6289,13 +6301,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B204" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B204" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="C204" s="4">
-        <v>985</v>
+        <v>485</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -6306,44 +6318,44 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="B205" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="B205" s="5" t="s">
-        <v>608</v>
-      </c>
       <c r="C205" s="6">
         <v>0</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="B206" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="B206" s="3" t="s">
-        <v>610</v>
-      </c>
       <c r="C206" s="4">
         <v>0</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="B207" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>612</v>
       </c>
       <c r="C207" s="6">
         <v>1000</v>
@@ -6357,10 +6369,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B208" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="C208" s="4">
         <v>112</v>
@@ -6374,10 +6386,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B209" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="C209" s="6">
         <v>402</v>
@@ -6386,49 +6398,49 @@
         <v>3</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="B210" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="B210" s="3" t="s">
-        <v>614</v>
-      </c>
       <c r="C210" s="4">
         <v>0</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="B211" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="B211" s="5" t="s">
-        <v>616</v>
-      </c>
       <c r="C211" s="6">
         <v>0</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B212" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="C212" s="4">
         <v>54</v>
@@ -6437,49 +6449,49 @@
         <v>3</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="B213" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="B213" s="5" t="s">
-        <v>618</v>
-      </c>
       <c r="C213" s="6">
         <v>0</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B214" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B214" s="3" t="s">
-        <v>620</v>
-      </c>
       <c r="C214" s="4">
         <v>0</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B215" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="C215" s="6">
         <v>345</v>
@@ -6493,44 +6505,44 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B216" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B216" s="3" t="s">
-        <v>622</v>
-      </c>
       <c r="C216" s="4">
         <v>0</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B217" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="B217" s="5" t="s">
-        <v>624</v>
-      </c>
       <c r="C217" s="6">
         <v>0</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B218" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="C218" s="4">
         <v>556</v>
@@ -6544,10 +6556,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B219" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B219" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="C219" s="6">
         <v>610</v>
@@ -6561,10 +6573,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B220" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="C220" s="4">
         <v>322</v>
@@ -6578,27 +6590,27 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="B221" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="B221" s="5" t="s">
-        <v>626</v>
-      </c>
       <c r="C221" s="6">
         <v>0</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B222" s="3" t="s">
         <v>627</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>628</v>
       </c>
       <c r="C222" s="4">
         <v>138</v>
@@ -6612,61 +6624,61 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="B223" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="B223" s="5" t="s">
-        <v>630</v>
-      </c>
       <c r="C223" s="6">
         <v>0</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="B224" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>632</v>
-      </c>
       <c r="C224" s="4">
         <v>0</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="B225" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="B225" s="5" t="s">
-        <v>634</v>
-      </c>
       <c r="C225" s="6">
         <v>0</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B226" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="C226" s="4">
         <v>604</v>
@@ -6680,10 +6692,10 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B227" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="C227" s="6">
         <v>1616</v>
@@ -6697,27 +6709,27 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B228" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B228" s="3" t="s">
-        <v>636</v>
-      </c>
       <c r="C228" s="4">
         <v>0</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B229" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="B229" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="C229" s="6">
         <v>2052</v>
@@ -6731,10 +6743,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B230" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="C230" s="4">
         <v>1262</v>
@@ -6748,61 +6760,61 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="B231" s="5" t="s">
         <v>637</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>638</v>
       </c>
       <c r="C231" s="6">
         <v>1013</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B232" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B232" s="3" t="s">
-        <v>640</v>
-      </c>
       <c r="C232" s="4">
         <v>0</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="B233" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>642</v>
       </c>
       <c r="C233" s="6">
         <v>500</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B234" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="C234" s="4">
         <v>800</v>
@@ -6816,10 +6828,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B235" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="C235" s="6">
         <v>198</v>
@@ -6833,44 +6845,44 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B236" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B236" s="3" t="s">
-        <v>644</v>
-      </c>
       <c r="C236" s="4">
         <v>0</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="B237" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="B237" s="5" t="s">
-        <v>646</v>
-      </c>
       <c r="C237" s="6">
         <v>0</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B238" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="C238" s="4">
         <v>618</v>
@@ -6884,95 +6896,95 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="B239" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="B239" s="5" t="s">
-        <v>648</v>
-      </c>
       <c r="C239" s="6">
         <v>0</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B240" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="B240" s="3" t="s">
-        <v>650</v>
-      </c>
       <c r="C240" s="4">
         <v>0</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="B241" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="B241" s="5" t="s">
-        <v>652</v>
-      </c>
       <c r="C241" s="6">
         <v>0</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B242" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="B242" s="3" t="s">
-        <v>654</v>
-      </c>
       <c r="C242" s="4">
         <v>0</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B243" s="5" t="s">
         <v>655</v>
       </c>
-      <c r="B243" s="5" t="s">
-        <v>656</v>
-      </c>
       <c r="C243" s="6">
         <v>0</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B244" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="C244" s="4">
         <v>800</v>
@@ -6986,10 +6998,10 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B245" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="B245" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="C245" s="6">
         <v>210</v>
@@ -7003,27 +7015,27 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B246" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="B246" s="3" t="s">
-        <v>658</v>
-      </c>
       <c r="C246" s="4">
         <v>0</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B247" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="B247" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="C247" s="6">
         <v>598</v>
@@ -7037,10 +7049,10 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B248" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="C248" s="4">
         <v>462</v>
@@ -7054,78 +7066,78 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="B249" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="B249" s="5" t="s">
-        <v>660</v>
-      </c>
       <c r="C249" s="6">
         <v>0</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B250" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="B250" s="3" t="s">
-        <v>662</v>
-      </c>
       <c r="C250" s="4">
         <v>0</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="B251" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="B251" s="5" t="s">
-        <v>664</v>
-      </c>
       <c r="C251" s="6">
         <v>0</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B252" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>666</v>
       </c>
       <c r="C252" s="4">
         <v>1000</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B253" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="B253" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="C253" s="6">
         <v>956</v>
@@ -7139,10 +7151,10 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B254" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="C254" s="4">
         <v>401</v>
@@ -7156,44 +7168,44 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="B255" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="B255" s="5" t="s">
-        <v>668</v>
-      </c>
       <c r="C255" s="6">
         <v>0</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B256" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B256" s="3" t="s">
-        <v>670</v>
-      </c>
       <c r="C256" s="4">
         <v>0</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B257" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>224</v>
       </c>
       <c r="C257" s="6">
         <v>248</v>
@@ -7207,10 +7219,10 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B258" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="C258" s="4">
         <v>675</v>
@@ -7224,27 +7236,27 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="B259" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="B259" s="5" t="s">
-        <v>672</v>
-      </c>
       <c r="C259" s="6">
         <v>0</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B260" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="C260" s="4">
         <v>605</v>
@@ -7258,10 +7270,10 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B261" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="B261" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="C261" s="6">
         <v>542</v>
@@ -7275,10 +7287,10 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B262" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="C262" s="4">
         <v>1079</v>
@@ -7292,10 +7304,10 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B263" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="C263" s="6">
         <v>458</v>
@@ -7309,27 +7321,27 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="B264" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B264" s="3" t="s">
-        <v>674</v>
-      </c>
       <c r="C264" s="4">
         <v>0</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B265" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="C265" s="6">
         <v>150</v>
@@ -7343,10 +7355,10 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B266" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="C266" s="4">
         <v>470</v>
@@ -7355,83 +7367,83 @@
         <v>3</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="B267" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="B267" s="5" t="s">
-        <v>676</v>
-      </c>
       <c r="C267" s="6">
         <v>0</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B268" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B268" s="3" t="s">
-        <v>678</v>
-      </c>
       <c r="C268" s="4">
         <v>0</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="B269" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="B269" s="5" t="s">
-        <v>680</v>
-      </c>
       <c r="C269" s="6">
         <v>0</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B270" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B270" s="3" t="s">
-        <v>682</v>
-      </c>
       <c r="C270" s="4">
         <v>0</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B271" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="B271" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="C271" s="6">
         <v>708</v>
@@ -7445,10 +7457,10 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B272" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="C272" s="4">
         <v>109</v>
@@ -7457,49 +7469,49 @@
         <v>3</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B273" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="B273" s="5" t="s">
-        <v>684</v>
-      </c>
       <c r="C273" s="6">
         <v>0</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B274" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="C274" s="4">
         <v>3367</v>
       </c>
       <c r="D274" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E274" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="E274" s="3" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B275" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="C275" s="6">
         <v>300</v>
@@ -7513,44 +7525,44 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="B276" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B276" s="3" t="s">
-        <v>686</v>
-      </c>
       <c r="C276" s="4">
         <v>0</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="B277" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="B277" s="5" t="s">
-        <v>688</v>
-      </c>
       <c r="C277" s="6">
         <v>0</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B278" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="B278" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="C278" s="4">
         <v>603</v>
@@ -7564,10 +7576,10 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B279" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="C279" s="6">
         <v>1299</v>
@@ -7581,27 +7593,27 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B280" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="B280" s="3" t="s">
-        <v>690</v>
-      </c>
       <c r="C280" s="4">
         <v>0</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B281" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="B281" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="C281" s="6">
         <v>800</v>
@@ -7615,27 +7627,27 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="B282" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="B282" s="3" t="s">
-        <v>692</v>
-      </c>
       <c r="C282" s="4">
         <v>0</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B283" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="B283" s="5" t="s">
-        <v>254</v>
       </c>
       <c r="C283" s="6">
         <v>1605</v>
@@ -7644,15 +7656,15 @@
         <v>3</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B284" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="C284" s="4">
         <v>618</v>
@@ -7666,27 +7678,27 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="B285" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="B285" s="5" t="s">
-        <v>694</v>
-      </c>
       <c r="C285" s="6">
         <v>0</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B286" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B286" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="C286" s="4">
         <v>754</v>
@@ -7700,10 +7712,10 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B287" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="B287" s="5" t="s">
-        <v>260</v>
       </c>
       <c r="C287" s="6">
         <v>148</v>
@@ -7717,112 +7729,112 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="B288" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="B288" s="3" t="s">
-        <v>696</v>
-      </c>
       <c r="C288" s="4">
         <v>0</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="B289" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="B289" s="5" t="s">
-        <v>698</v>
-      </c>
       <c r="C289" s="6">
         <v>0</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B290" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="B290" s="3" t="s">
-        <v>700</v>
-      </c>
       <c r="C290" s="4">
         <v>0</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B291" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="B291" s="5" t="s">
-        <v>702</v>
-      </c>
       <c r="C291" s="6">
         <v>0</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B292" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="B292" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="C292" s="4">
         <v>500</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="B293" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="B293" s="5" t="s">
-        <v>706</v>
-      </c>
       <c r="C293" s="6">
         <v>0</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B294" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="B294" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="C294" s="4">
         <v>1735</v>
@@ -7836,10 +7848,10 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B295" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="C295" s="6">
         <v>811</v>
@@ -7853,27 +7865,27 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="B296" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B296" s="3" t="s">
-        <v>708</v>
-      </c>
       <c r="C296" s="4">
         <v>0</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B297" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="B297" s="5" t="s">
-        <v>266</v>
       </c>
       <c r="C297" s="6">
         <v>717</v>
@@ -7887,27 +7899,27 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B298" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="B298" s="3" t="s">
-        <v>710</v>
-      </c>
       <c r="C298" s="4">
         <v>0</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B299" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="B299" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="C299" s="6">
         <v>257</v>
@@ -7921,10 +7933,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B300" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B300" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="C300" s="4">
         <v>31</v>
@@ -7938,10 +7950,10 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="B301" s="5" t="s">
         <v>711</v>
-      </c>
-      <c r="B301" s="5" t="s">
-        <v>712</v>
       </c>
       <c r="C301" s="6">
         <v>1000</v>
@@ -7955,10 +7967,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B302" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="C302" s="4">
         <v>649</v>
@@ -7972,27 +7984,27 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="B303" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="B303" s="5" t="s">
-        <v>714</v>
-      </c>
       <c r="C303" s="6">
         <v>0</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B304" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="B304" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="C304" s="4">
         <v>200</v>
@@ -8006,10 +8018,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B305" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B305" s="5" t="s">
-        <v>276</v>
       </c>
       <c r="C305" s="6">
         <v>280</v>
@@ -8023,27 +8035,27 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B306" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="B306" s="3" t="s">
-        <v>716</v>
-      </c>
       <c r="C306" s="4">
         <v>0</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B307" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="B307" s="5" t="s">
-        <v>278</v>
       </c>
       <c r="C307" s="6">
         <v>0</v>
@@ -8057,10 +8069,10 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B308" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B308" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="C308" s="4">
         <v>389</v>
@@ -8074,27 +8086,27 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="B309" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="B309" s="5" t="s">
-        <v>718</v>
-      </c>
       <c r="C309" s="6">
         <v>0</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E309" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B310" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="C310" s="4">
         <v>5</v>
@@ -8108,10 +8120,10 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B311" s="5" t="s">
         <v>283</v>
-      </c>
-      <c r="B311" s="5" t="s">
-        <v>284</v>
       </c>
       <c r="C311" s="6">
         <v>503</v>
@@ -8125,10 +8137,10 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B312" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="B312" s="3" t="s">
-        <v>286</v>
       </c>
       <c r="C312" s="4">
         <v>987</v>
@@ -8142,27 +8154,27 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B313" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="B313" s="5" t="s">
-        <v>720</v>
-      </c>
       <c r="C313" s="6">
         <v>0</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B314" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="B314" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="C314" s="4">
         <v>600</v>
@@ -8176,27 +8188,27 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="B315" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="B315" s="5" t="s">
-        <v>722</v>
-      </c>
       <c r="C315" s="6">
         <v>0</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B316" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="B316" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="C316" s="4">
         <v>812</v>
@@ -8210,10 +8222,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B317" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="B317" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="C317" s="6">
         <v>1152</v>
@@ -8227,10 +8239,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B318" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="B318" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="C318" s="4">
         <v>477</v>
@@ -8244,10 +8256,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B319" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="B319" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="C319" s="6">
         <v>686</v>
@@ -8261,95 +8273,95 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B320" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="C320" s="4">
         <v>3351</v>
       </c>
       <c r="D320" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E320" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="E320" s="3" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="B321" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="B321" s="5" t="s">
-        <v>724</v>
-      </c>
       <c r="C321" s="6">
         <v>0</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="B322" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B322" s="3" t="s">
-        <v>726</v>
-      </c>
       <c r="C322" s="4">
         <v>0</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="B323" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="B323" s="5" t="s">
-        <v>728</v>
-      </c>
       <c r="C323" s="6">
         <v>0</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B324" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="B324" s="3" t="s">
-        <v>730</v>
-      </c>
       <c r="C324" s="4">
         <v>0</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B325" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="B325" s="5" t="s">
-        <v>300</v>
       </c>
       <c r="C325" s="6">
         <v>0</v>
@@ -8358,15 +8370,15 @@
         <v>3</v>
       </c>
       <c r="E325" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B326" s="3" t="s">
         <v>731</v>
-      </c>
-      <c r="B326" s="3" t="s">
-        <v>732</v>
       </c>
       <c r="C326" s="4">
         <v>190</v>
@@ -8380,10 +8392,10 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B327" s="5" t="s">
         <v>301</v>
-      </c>
-      <c r="B327" s="5" t="s">
-        <v>302</v>
       </c>
       <c r="C327" s="6">
         <v>1694</v>
@@ -8397,27 +8409,27 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B328" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="B328" s="3" t="s">
-        <v>734</v>
-      </c>
       <c r="C328" s="4">
         <v>0</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B329" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="B329" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="C329" s="6">
         <v>610</v>
@@ -8431,10 +8443,10 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B330" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="C330" s="4">
         <v>385</v>
@@ -8448,10 +8460,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B331" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="B331" s="5" t="s">
-        <v>308</v>
       </c>
       <c r="C331" s="6">
         <v>397</v>
@@ -8465,10 +8477,10 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B332" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="B332" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="C332" s="4">
         <v>1500</v>
@@ -8482,61 +8494,61 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="B333" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="B333" s="5" t="s">
-        <v>736</v>
-      </c>
       <c r="C333" s="6">
         <v>0</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E333" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B334" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B334" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="C334" s="4">
-        <v>709</v>
+        <v>1199</v>
       </c>
       <c r="D334" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E334" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="E334" s="3" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B335" s="5" t="s">
         <v>313</v>
-      </c>
-      <c r="B335" s="5" t="s">
-        <v>314</v>
       </c>
       <c r="C335" s="6">
         <v>17</v>
       </c>
       <c r="D335" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E335" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E335" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B336" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="B336" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="C336" s="4">
         <v>697</v>
@@ -8550,44 +8562,44 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="B337" s="5" t="s">
         <v>737</v>
-      </c>
-      <c r="B337" s="5" t="s">
-        <v>738</v>
       </c>
       <c r="C337" s="6">
         <v>244</v>
       </c>
       <c r="D337" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E337" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E337" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B338" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="B338" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="C338" s="4">
         <v>6216</v>
       </c>
       <c r="D338" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E338" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="E338" s="3" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B339" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="B339" s="5" t="s">
-        <v>320</v>
       </c>
       <c r="C339" s="6">
         <v>0</v>
@@ -8601,61 +8613,61 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B340" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="B340" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="C340" s="4">
         <v>184</v>
       </c>
       <c r="D340" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E340" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="E340" s="3" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="B341" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="B341" s="5" t="s">
-        <v>740</v>
-      </c>
       <c r="C341" s="6">
         <v>0</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E341" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B342" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="B342" s="3" t="s">
-        <v>742</v>
-      </c>
       <c r="C342" s="4">
         <v>0</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B343" s="5" t="s">
         <v>323</v>
-      </c>
-      <c r="B343" s="5" t="s">
-        <v>324</v>
       </c>
       <c r="C343" s="6">
         <v>148</v>
@@ -8669,10 +8681,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B344" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="B344" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="C344" s="4">
         <v>466</v>
@@ -8686,10 +8698,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B345" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="B345" s="5" t="s">
-        <v>328</v>
       </c>
       <c r="C345" s="6">
         <v>291</v>
@@ -8703,10 +8715,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B346" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="B346" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="C346" s="4">
         <v>205</v>
@@ -8720,10 +8732,10 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B347" s="5" t="s">
         <v>331</v>
-      </c>
-      <c r="B347" s="5" t="s">
-        <v>332</v>
       </c>
       <c r="C347" s="6">
         <v>1007</v>
@@ -8737,27 +8749,27 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B348" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B348" s="3" t="s">
-        <v>744</v>
-      </c>
       <c r="C348" s="4">
         <v>0</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B349" s="5" t="s">
         <v>333</v>
-      </c>
-      <c r="B349" s="5" t="s">
-        <v>334</v>
       </c>
       <c r="C349" s="6">
         <v>1612</v>
@@ -8771,44 +8783,44 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B350" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="B350" s="3" t="s">
-        <v>746</v>
-      </c>
       <c r="C350" s="4">
         <v>0</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="B351" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="B351" s="5" t="s">
-        <v>748</v>
-      </c>
       <c r="C351" s="6">
         <v>0</v>
       </c>
       <c r="D351" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E351" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B352" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="B352" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="C352" s="4">
         <v>0</v>
@@ -8822,10 +8834,10 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B353" s="5" t="s">
         <v>337</v>
-      </c>
-      <c r="B353" s="5" t="s">
-        <v>338</v>
       </c>
       <c r="C353" s="6">
         <v>1766</v>
@@ -8839,10 +8851,10 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B354" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="B354" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="C354" s="4">
         <v>598</v>
@@ -8856,27 +8868,27 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B355" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="B355" s="5" t="s">
-        <v>750</v>
-      </c>
       <c r="C355" s="6">
         <v>0</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B356" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="B356" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="C356" s="4">
         <v>147</v>
@@ -8890,10 +8902,10 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B357" s="5" t="s">
         <v>343</v>
-      </c>
-      <c r="B357" s="5" t="s">
-        <v>344</v>
       </c>
       <c r="C357" s="6">
         <v>605</v>
@@ -8907,10 +8919,10 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B358" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="B358" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="C358" s="4">
         <v>322</v>
@@ -8924,61 +8936,61 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B359" s="5" t="s">
         <v>347</v>
-      </c>
-      <c r="B359" s="5" t="s">
-        <v>348</v>
       </c>
       <c r="C359" s="6">
         <v>320</v>
       </c>
       <c r="D359" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E359" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E359" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="B360" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="B360" s="3" t="s">
-        <v>752</v>
-      </c>
       <c r="C360" s="4">
         <v>0</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="B361" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="B361" s="5" t="s">
-        <v>754</v>
-      </c>
       <c r="C361" s="6">
         <v>0</v>
       </c>
       <c r="D361" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E361" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B362" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="B362" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="C362" s="4">
         <v>624</v>
@@ -8992,10 +9004,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B363" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="B363" s="5" t="s">
-        <v>352</v>
       </c>
       <c r="C363" s="6">
         <v>185</v>
@@ -9009,10 +9021,10 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B364" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="B364" s="3" t="s">
-        <v>354</v>
       </c>
       <c r="C364" s="4">
         <v>700</v>
@@ -9026,44 +9038,44 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B365" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="B365" s="5" t="s">
-        <v>756</v>
-      </c>
       <c r="C365" s="6">
         <v>0</v>
       </c>
       <c r="D365" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="B366" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="B366" s="3" t="s">
-        <v>758</v>
-      </c>
       <c r="C366" s="4">
         <v>0</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B367" s="5" t="s">
         <v>355</v>
-      </c>
-      <c r="B367" s="5" t="s">
-        <v>356</v>
       </c>
       <c r="C367" s="6">
         <v>603</v>
@@ -9077,10 +9089,10 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B368" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="B368" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="C368" s="4">
         <v>66</v>
@@ -9094,10 +9106,10 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B369" s="5" t="s">
         <v>359</v>
-      </c>
-      <c r="B369" s="5" t="s">
-        <v>360</v>
       </c>
       <c r="C369" s="6">
         <v>113</v>
@@ -9111,10 +9123,10 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B370" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="B370" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="C370" s="4">
         <v>159</v>
@@ -9128,27 +9140,27 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="B371" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="B371" s="5" t="s">
-        <v>760</v>
-      </c>
       <c r="C371" s="6">
         <v>0</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E371" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B372" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="B372" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="C372" s="4">
         <v>1054</v>
@@ -9162,44 +9174,44 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B373" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="B373" s="5" t="s">
-        <v>366</v>
       </c>
       <c r="C373" s="6">
         <v>90</v>
       </c>
       <c r="D373" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="E373" s="5" t="s">
         <v>779</v>
-      </c>
-      <c r="E373" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B374" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B374" s="3" t="s">
-        <v>762</v>
-      </c>
       <c r="C374" s="4">
         <v>0</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B375" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="B375" s="5" t="s">
-        <v>368</v>
       </c>
       <c r="C375" s="6">
         <v>12</v>
@@ -9213,44 +9225,44 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B376" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B376" s="3" t="s">
-        <v>764</v>
-      </c>
       <c r="C376" s="4">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="B377" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="B377" s="5" t="s">
-        <v>766</v>
-      </c>
       <c r="C377" s="6">
         <v>0</v>
       </c>
       <c r="D377" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B378" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="B378" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="C378" s="4">
         <v>749</v>
@@ -9264,27 +9276,27 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="B379" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="B379" s="5" t="s">
-        <v>768</v>
-      </c>
       <c r="C379" s="6">
         <v>0</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B380" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="B380" s="3" t="s">
-        <v>372</v>
       </c>
       <c r="C380" s="4">
         <v>2013</v>
@@ -9298,27 +9310,27 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="B381" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="B381" s="5" t="s">
-        <v>770</v>
-      </c>
       <c r="C381" s="6">
         <v>0</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B382" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="B382" s="3" t="s">
-        <v>374</v>
       </c>
       <c r="C382" s="4">
         <v>710</v>
@@ -9332,10 +9344,10 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B383" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="B383" s="5" t="s">
-        <v>376</v>
       </c>
       <c r="C383" s="6">
         <v>249</v>
@@ -9349,61 +9361,61 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B384" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="B384" s="3" t="s">
-        <v>772</v>
-      </c>
       <c r="C384" s="4">
         <v>0</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="B385" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="B385" s="5" t="s">
-        <v>774</v>
-      </c>
       <c r="C385" s="6">
         <v>0</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E385" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B386" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="B386" s="3" t="s">
-        <v>776</v>
-      </c>
       <c r="C386" s="4">
         <v>0</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B387" s="5" t="s">
         <v>377</v>
-      </c>
-      <c r="B387" s="5" t="s">
-        <v>378</v>
       </c>
       <c r="C387" s="6">
         <v>505</v>
@@ -9413,6 +9425,40 @@
       </c>
       <c r="E387" s="5">
         <v>3</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>783</v>
+      </c>
+      <c r="B388" t="s">
+        <v>784</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388" t="s">
+        <v>776</v>
+      </c>
+      <c r="E388" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>785</v>
+      </c>
+      <c r="B389" t="s">
+        <v>786</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389" t="s">
+        <v>776</v>
+      </c>
+      <c r="E389" t="s">
+        <v>776</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A255759-C31D-4E69-8245-C434A20F4D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42D41A1-27D0-4471-B888-B003410112EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -2992,7 +2992,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6">
-        <v>2867</v>
+        <v>2517</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -4267,7 +4267,7 @@
         <v>76</v>
       </c>
       <c r="C84" s="4">
-        <v>1383</v>
+        <v>1283</v>
       </c>
       <c r="D84" s="3">
         <v>3</v>
@@ -4743,7 +4743,7 @@
         <v>95</v>
       </c>
       <c r="C112" s="4">
-        <v>2003</v>
+        <v>1903</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -6069,7 +6069,7 @@
         <v>163</v>
       </c>
       <c r="C190" s="4">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6103,7 +6103,7 @@
         <v>599</v>
       </c>
       <c r="C192" s="4">
-        <v>1000</v>
+        <v>695</v>
       </c>
       <c r="D192" s="3">
         <v>3</v>
@@ -8245,7 +8245,7 @@
         <v>293</v>
       </c>
       <c r="C318" s="4">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="D318" s="3">
         <v>1</v>
@@ -8517,7 +8517,7 @@
         <v>311</v>
       </c>
       <c r="C334" s="4">
-        <v>1199</v>
+        <v>1099</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>778</v>
@@ -8738,7 +8738,7 @@
         <v>331</v>
       </c>
       <c r="C347" s="6">
-        <v>1007</v>
+        <v>687</v>
       </c>
       <c r="D347" s="5">
         <v>3</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42D41A1-27D0-4471-B888-B003410112EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4943246-2B1F-4F69-88AA-EFBF766E72CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -5202,7 +5202,7 @@
         <v>115</v>
       </c>
       <c r="C139" s="6">
-        <v>743</v>
+        <v>643</v>
       </c>
       <c r="D139" s="5">
         <v>5</v>
@@ -5695,7 +5695,7 @@
         <v>141</v>
       </c>
       <c r="C168" s="4">
-        <v>316</v>
+        <v>116</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -6256,7 +6256,7 @@
         <v>175</v>
       </c>
       <c r="C201" s="6">
-        <v>1202</v>
+        <v>942</v>
       </c>
       <c r="D201" s="5">
         <v>5</v>
@@ -6307,7 +6307,7 @@
         <v>181</v>
       </c>
       <c r="C204" s="4">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -7276,7 +7276,7 @@
         <v>229</v>
       </c>
       <c r="C261" s="6">
-        <v>542</v>
+        <v>442</v>
       </c>
       <c r="D261" s="5">
         <v>3</v>
@@ -9231,7 +9231,7 @@
         <v>763</v>
       </c>
       <c r="C376" s="4">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>776</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4943246-2B1F-4F69-88AA-EFBF766E72CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD83164-6B63-426D-8D42-0FB9D5A00384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="789">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -2396,6 +2396,12 @@
   </si>
   <si>
     <t>0388-U</t>
+  </si>
+  <si>
+    <t>فريز - للجنسين</t>
+  </si>
+  <si>
+    <t>0389-U</t>
   </si>
 </sst>
 </file>
@@ -2838,7 +2844,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E389"/>
+  <dimension ref="A1:E390"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.26953125" bestFit="1" customWidth="1"/>
@@ -5032,7 +5038,7 @@
         <v>109</v>
       </c>
       <c r="C129" s="6">
-        <v>50</v>
+        <v>2050</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>778</v>
@@ -5491,7 +5497,7 @@
         <v>561</v>
       </c>
       <c r="C156" s="4">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>776</v>
@@ -6630,7 +6636,7 @@
         <v>629</v>
       </c>
       <c r="C223" s="6">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>776</v>
@@ -8058,7 +8064,7 @@
         <v>277</v>
       </c>
       <c r="C307" s="6">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="D307" s="5">
         <v>5</v>
@@ -8823,7 +8829,7 @@
         <v>335</v>
       </c>
       <c r="C352" s="4">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>
@@ -9458,6 +9464,23 @@
         <v>776</v>
       </c>
       <c r="E389" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>787</v>
+      </c>
+      <c r="B390" t="s">
+        <v>788</v>
+      </c>
+      <c r="C390">
+        <v>2000</v>
+      </c>
+      <c r="D390" t="s">
+        <v>776</v>
+      </c>
+      <c r="E390" t="s">
         <v>776</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD83164-6B63-426D-8D42-0FB9D5A00384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17D18A8-D1C1-4B5E-A86D-5735E1AFE29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -5038,7 +5038,7 @@
         <v>109</v>
       </c>
       <c r="C129" s="6">
-        <v>2050</v>
+        <v>1550</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>778</v>
@@ -5497,7 +5497,7 @@
         <v>561</v>
       </c>
       <c r="C156" s="4">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>776</v>
@@ -6109,7 +6109,7 @@
         <v>599</v>
       </c>
       <c r="C192" s="4">
-        <v>695</v>
+        <v>395</v>
       </c>
       <c r="D192" s="3">
         <v>3</v>
@@ -6636,7 +6636,7 @@
         <v>629</v>
       </c>
       <c r="C223" s="6">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>776</v>
@@ -8319,7 +8319,7 @@
         <v>725</v>
       </c>
       <c r="C322" s="4">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>776</v>
@@ -8829,7 +8829,7 @@
         <v>335</v>
       </c>
       <c r="C352" s="4">
-        <v>5000</v>
+        <v>3834</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>
@@ -9475,7 +9475,7 @@
         <v>788</v>
       </c>
       <c r="C390">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D390" t="s">
         <v>776</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17D18A8-D1C1-4B5E-A86D-5735E1AFE29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098D9E30-3831-40DA-9DF5-6B3C0620EF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -4749,7 +4749,7 @@
         <v>95</v>
       </c>
       <c r="C112" s="4">
-        <v>1903</v>
+        <v>1403</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -6143,7 +6143,7 @@
         <v>167</v>
       </c>
       <c r="C194" s="4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D194" s="3">
         <v>3</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098D9E30-3831-40DA-9DF5-6B3C0620EF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C309585-492A-4524-AA3F-17B913BF2FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -5208,7 +5208,7 @@
         <v>115</v>
       </c>
       <c r="C139" s="6">
-        <v>643</v>
+        <v>518</v>
       </c>
       <c r="D139" s="5">
         <v>5</v>
@@ -6313,7 +6313,7 @@
         <v>181</v>
       </c>
       <c r="C204" s="4">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C309585-492A-4524-AA3F-17B913BF2FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73B8FE8-75E6-4D35-AF39-577FDCF10997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -5701,7 +5701,7 @@
         <v>141</v>
       </c>
       <c r="C168" s="4">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -6551,7 +6551,7 @@
         <v>191</v>
       </c>
       <c r="C218" s="4">
-        <v>556</v>
+        <v>356</v>
       </c>
       <c r="D218" s="3">
         <v>3</v>
@@ -6568,7 +6568,7 @@
         <v>193</v>
       </c>
       <c r="C219" s="6">
-        <v>610</v>
+        <v>360</v>
       </c>
       <c r="D219" s="5">
         <v>5</v>
@@ -7843,7 +7843,7 @@
         <v>261</v>
       </c>
       <c r="C294" s="4">
-        <v>1735</v>
+        <v>1435</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -8744,7 +8744,7 @@
         <v>331</v>
       </c>
       <c r="C347" s="6">
-        <v>687</v>
+        <v>487</v>
       </c>
       <c r="D347" s="5">
         <v>3</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73B8FE8-75E6-4D35-AF39-577FDCF10997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79498E3B-997A-4CC1-8ABA-4C74B7296F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="792">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -2402,6 +2402,15 @@
   </si>
   <si>
     <t>0389-U</t>
+  </si>
+  <si>
+    <t>مانجا - للجنسين</t>
+  </si>
+  <si>
+    <t>ورد دمشقي - للجنسين</t>
+  </si>
+  <si>
+    <t>نسيم البحر - للجنسين</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2853,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E390"/>
+  <dimension ref="A1:E393"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.26953125" bestFit="1" customWidth="1"/>
@@ -3899,7 +3908,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="4">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D62" s="3">
         <v>3</v>
@@ -4749,7 +4758,7 @@
         <v>95</v>
       </c>
       <c r="C112" s="4">
-        <v>1403</v>
+        <v>893</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -6109,7 +6118,7 @@
         <v>599</v>
       </c>
       <c r="C192" s="4">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="D192" s="3">
         <v>3</v>
@@ -6177,7 +6186,7 @@
         <v>171</v>
       </c>
       <c r="C196" s="4">
-        <v>2118</v>
+        <v>2007</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6568,7 +6577,7 @@
         <v>193</v>
       </c>
       <c r="C219" s="6">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D219" s="5">
         <v>5</v>
@@ -9254,7 +9263,7 @@
         <v>765</v>
       </c>
       <c r="C377" s="6">
-        <v>0</v>
+        <v>1878</v>
       </c>
       <c r="D377" s="5" t="s">
         <v>776</v>
@@ -9481,6 +9490,57 @@
         <v>776</v>
       </c>
       <c r="E390" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>789</v>
+      </c>
+      <c r="B391" t="s">
+        <v>788</v>
+      </c>
+      <c r="C391">
+        <v>1000</v>
+      </c>
+      <c r="D391" t="s">
+        <v>776</v>
+      </c>
+      <c r="E391" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>790</v>
+      </c>
+      <c r="B392" t="s">
+        <v>788</v>
+      </c>
+      <c r="C392">
+        <v>1000</v>
+      </c>
+      <c r="D392" t="s">
+        <v>776</v>
+      </c>
+      <c r="E392" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>791</v>
+      </c>
+      <c r="B393" t="s">
+        <v>788</v>
+      </c>
+      <c r="C393">
+        <v>1000</v>
+      </c>
+      <c r="D393" t="s">
+        <v>776</v>
+      </c>
+      <c r="E393" t="s">
         <v>776</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79498E3B-997A-4CC1-8ABA-4C74B7296F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5392C1C-6BE4-4E59-ABC9-A055E437D2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3330,7 +3330,7 @@
         <v>30</v>
       </c>
       <c r="C28" s="4">
-        <v>634</v>
+        <v>294</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -3449,7 +3449,7 @@
         <v>40</v>
       </c>
       <c r="C35" s="6">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="D35" s="5">
         <v>3</v>
@@ -3483,7 +3483,7 @@
         <v>44</v>
       </c>
       <c r="C37" s="6">
-        <v>1470</v>
+        <v>1182</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -4078,7 +4078,7 @@
         <v>68</v>
       </c>
       <c r="C72" s="4">
-        <v>710</v>
+        <v>470</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -4214,7 +4214,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D80" s="3">
         <v>4</v>
@@ -4316,7 +4316,7 @@
         <v>80</v>
       </c>
       <c r="C86" s="4">
-        <v>2665</v>
+        <v>2345</v>
       </c>
       <c r="D86" s="3">
         <v>3</v>
@@ -4962,7 +4962,7 @@
         <v>521</v>
       </c>
       <c r="C124" s="4">
-        <v>550</v>
+        <v>278</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>776</v>
@@ -5574,7 +5574,7 @@
         <v>133</v>
       </c>
       <c r="C160" s="4">
-        <v>1476</v>
+        <v>1165</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -6084,7 +6084,7 @@
         <v>163</v>
       </c>
       <c r="C190" s="4">
-        <v>1800</v>
+        <v>1484</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -7070,7 +7070,7 @@
         <v>217</v>
       </c>
       <c r="C248" s="4">
-        <v>462</v>
+        <v>199</v>
       </c>
       <c r="D248" s="3">
         <v>4</v>
@@ -7597,7 +7597,7 @@
         <v>249</v>
       </c>
       <c r="C279" s="6">
-        <v>1299</v>
+        <v>1089</v>
       </c>
       <c r="D279" s="5">
         <v>2</v>
@@ -7682,7 +7682,7 @@
         <v>255</v>
       </c>
       <c r="C284" s="4">
-        <v>618</v>
+        <v>303</v>
       </c>
       <c r="D284" s="3">
         <v>1</v>
@@ -7852,7 +7852,7 @@
         <v>261</v>
       </c>
       <c r="C294" s="4">
-        <v>1435</v>
+        <v>765</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -8073,7 +8073,7 @@
         <v>277</v>
       </c>
       <c r="C307" s="6">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D307" s="5">
         <v>5</v>
@@ -8583,7 +8583,7 @@
         <v>737</v>
       </c>
       <c r="C337" s="6">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="D337" s="5" t="s">
         <v>778</v>
@@ -8838,7 +8838,7 @@
         <v>335</v>
       </c>
       <c r="C352" s="4">
-        <v>3834</v>
+        <v>3284</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>
@@ -8872,7 +8872,7 @@
         <v>339</v>
       </c>
       <c r="C354" s="4">
-        <v>598</v>
+        <v>282</v>
       </c>
       <c r="D354" s="3">
         <v>2</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5392C1C-6BE4-4E59-ABC9-A055E437D2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01A5821-7462-4AF6-84D5-A9532321C84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="795">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -2411,6 +2411,15 @@
   </si>
   <si>
     <t>نسيم البحر - للجنسين</t>
+  </si>
+  <si>
+    <t>0390-U</t>
+  </si>
+  <si>
+    <t>0391-U</t>
+  </si>
+  <si>
+    <t>0392-U</t>
   </si>
 </sst>
 </file>
@@ -2888,7 +2897,7 @@
         <v>379</v>
       </c>
       <c r="C2" s="4">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>776</v>
@@ -2905,7 +2914,7 @@
         <v>381</v>
       </c>
       <c r="C3" s="6">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>776</v>
@@ -2922,7 +2931,7 @@
         <v>383</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>776</v>
@@ -2939,7 +2948,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="6">
-        <v>235</v>
+        <v>629</v>
       </c>
       <c r="D5" s="5">
         <v>5</v>
@@ -2956,7 +2965,7 @@
         <v>385</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>776</v>
@@ -2973,7 +2982,7 @@
         <v>387</v>
       </c>
       <c r="C7" s="6">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>776</v>
@@ -2990,7 +2999,7 @@
         <v>389</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>776</v>
@@ -3007,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6">
-        <v>2517</v>
+        <v>2778</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -3024,7 +3033,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="4">
-        <v>374</v>
+        <v>564</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -3041,7 +3050,7 @@
         <v>391</v>
       </c>
       <c r="C11" s="6">
-        <v>0</v>
+        <v>2127</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>776</v>
@@ -3058,7 +3067,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="4">
-        <v>1229</v>
+        <v>1600</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -3075,7 +3084,7 @@
         <v>393</v>
       </c>
       <c r="C13" s="6">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>776</v>
@@ -3092,7 +3101,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="4">
-        <v>371</v>
+        <v>811</v>
       </c>
       <c r="D14" s="3">
         <v>3</v>
@@ -3109,7 +3118,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="6">
-        <v>562</v>
+        <v>1216</v>
       </c>
       <c r="D15" s="5">
         <v>5</v>
@@ -3126,7 +3135,7 @@
         <v>395</v>
       </c>
       <c r="C16" s="4">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>776</v>
@@ -3160,7 +3169,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="4">
-        <v>361</v>
+        <v>582</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -3194,7 +3203,7 @@
         <v>399</v>
       </c>
       <c r="C20" s="4">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>776</v>
@@ -3262,7 +3271,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="4">
-        <v>1190</v>
+        <v>1546</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -3279,7 +3288,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="6">
-        <v>703</v>
+        <v>964</v>
       </c>
       <c r="D25" s="5">
         <v>2</v>
@@ -3296,7 +3305,7 @@
         <v>28</v>
       </c>
       <c r="C26" s="4">
-        <v>455</v>
+        <v>704</v>
       </c>
       <c r="D26" s="3">
         <v>3</v>
@@ -3313,7 +3322,7 @@
         <v>405</v>
       </c>
       <c r="C27" s="6">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>776</v>
@@ -3330,7 +3339,7 @@
         <v>30</v>
       </c>
       <c r="C28" s="4">
-        <v>294</v>
+        <v>429</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -3347,7 +3356,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="6">
-        <v>899</v>
+        <v>1126</v>
       </c>
       <c r="D29" s="5">
         <v>3</v>
@@ -3364,7 +3373,7 @@
         <v>407</v>
       </c>
       <c r="C30" s="4">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>776</v>
@@ -3381,7 +3390,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="6">
-        <v>1000</v>
+        <v>1430</v>
       </c>
       <c r="D31" s="5">
         <v>3</v>
@@ -3398,7 +3407,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="4">
-        <v>534</v>
+        <v>706</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -3415,7 +3424,7 @@
         <v>38</v>
       </c>
       <c r="C33" s="6">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D33" s="5">
         <v>2</v>
@@ -3432,7 +3441,7 @@
         <v>409</v>
       </c>
       <c r="C34" s="4">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>776</v>
@@ -3449,7 +3458,7 @@
         <v>40</v>
       </c>
       <c r="C35" s="6">
-        <v>1</v>
+        <v>348</v>
       </c>
       <c r="D35" s="5">
         <v>3</v>
@@ -3466,7 +3475,7 @@
         <v>42</v>
       </c>
       <c r="C36" s="4">
-        <v>218</v>
+        <v>629</v>
       </c>
       <c r="D36" s="3">
         <v>4</v>
@@ -3483,7 +3492,7 @@
         <v>44</v>
       </c>
       <c r="C37" s="6">
-        <v>1182</v>
+        <v>1614</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -3500,7 +3509,7 @@
         <v>411</v>
       </c>
       <c r="C38" s="4">
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>776</v>
@@ -3517,7 +3526,7 @@
         <v>413</v>
       </c>
       <c r="C39" s="6">
-        <v>900</v>
+        <v>1103</v>
       </c>
       <c r="D39" s="5">
         <v>3</v>
@@ -3534,7 +3543,7 @@
         <v>415</v>
       </c>
       <c r="C40" s="4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>776</v>
@@ -3551,7 +3560,7 @@
         <v>417</v>
       </c>
       <c r="C41" s="6">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>776</v>
@@ -3568,7 +3577,7 @@
         <v>46</v>
       </c>
       <c r="C42" s="4">
-        <v>357</v>
+        <v>852</v>
       </c>
       <c r="D42" s="3">
         <v>2</v>
@@ -3585,7 +3594,7 @@
         <v>48</v>
       </c>
       <c r="C43" s="6">
-        <v>699</v>
+        <v>1002</v>
       </c>
       <c r="D43" s="5">
         <v>6</v>
@@ -3602,7 +3611,7 @@
         <v>419</v>
       </c>
       <c r="C44" s="4">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>776</v>
@@ -3619,7 +3628,7 @@
         <v>50</v>
       </c>
       <c r="C45" s="6">
-        <v>707</v>
+        <v>828</v>
       </c>
       <c r="D45" s="5">
         <v>6</v>
@@ -3636,7 +3645,7 @@
         <v>421</v>
       </c>
       <c r="C46" s="4">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>776</v>
@@ -3653,7 +3662,7 @@
         <v>52</v>
       </c>
       <c r="C47" s="6">
-        <v>1002</v>
+        <v>1268</v>
       </c>
       <c r="D47" s="5">
         <v>2</v>
@@ -3670,7 +3679,7 @@
         <v>423</v>
       </c>
       <c r="C48" s="4">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>776</v>
@@ -3687,7 +3696,7 @@
         <v>425</v>
       </c>
       <c r="C49" s="6">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>776</v>
@@ -3704,7 +3713,7 @@
         <v>54</v>
       </c>
       <c r="C50" s="4">
-        <v>583</v>
+        <v>1009</v>
       </c>
       <c r="D50" s="3">
         <v>3</v>
@@ -3721,7 +3730,7 @@
         <v>56</v>
       </c>
       <c r="C51" s="6">
-        <v>710</v>
+        <v>1000</v>
       </c>
       <c r="D51" s="5">
         <v>5</v>
@@ -3755,7 +3764,7 @@
         <v>429</v>
       </c>
       <c r="C53" s="6">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>776</v>
@@ -3772,7 +3781,7 @@
         <v>431</v>
       </c>
       <c r="C54" s="4">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>776</v>
@@ -3789,7 +3798,7 @@
         <v>433</v>
       </c>
       <c r="C55" s="6">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>776</v>
@@ -3806,7 +3815,7 @@
         <v>435</v>
       </c>
       <c r="C56" s="4">
-        <v>500</v>
+        <v>734</v>
       </c>
       <c r="D56" s="3">
         <v>5</v>
@@ -3823,7 +3832,7 @@
         <v>437</v>
       </c>
       <c r="C57" s="6">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>776</v>
@@ -3840,7 +3849,7 @@
         <v>439</v>
       </c>
       <c r="C58" s="4">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>776</v>
@@ -3857,7 +3866,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="6">
-        <v>700</v>
+        <v>1058</v>
       </c>
       <c r="D59" s="5">
         <v>6</v>
@@ -3874,7 +3883,7 @@
         <v>441</v>
       </c>
       <c r="C60" s="4">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>776</v>
@@ -3891,7 +3900,7 @@
         <v>443</v>
       </c>
       <c r="C61" s="6">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>776</v>
@@ -3908,7 +3917,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="4">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="D62" s="3">
         <v>3</v>
@@ -3925,7 +3934,7 @@
         <v>445</v>
       </c>
       <c r="C63" s="6">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>776</v>
@@ -3942,7 +3951,7 @@
         <v>62</v>
       </c>
       <c r="C64" s="4">
-        <v>713</v>
+        <v>1090</v>
       </c>
       <c r="D64" s="3">
         <v>2</v>
@@ -3959,7 +3968,7 @@
         <v>447</v>
       </c>
       <c r="C65" s="6">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>776</v>
@@ -3976,7 +3985,7 @@
         <v>64</v>
       </c>
       <c r="C66" s="4">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="D66" s="3">
         <v>3</v>
@@ -3993,7 +4002,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="6">
-        <v>413</v>
+        <v>698</v>
       </c>
       <c r="D67" s="5">
         <v>5</v>
@@ -4010,7 +4019,7 @@
         <v>449</v>
       </c>
       <c r="C68" s="4">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>776</v>
@@ -4027,7 +4036,7 @@
         <v>451</v>
       </c>
       <c r="C69" s="6">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>776</v>
@@ -4061,7 +4070,7 @@
         <v>455</v>
       </c>
       <c r="C71" s="6">
-        <v>847</v>
+        <v>1112</v>
       </c>
       <c r="D71" s="5">
         <v>2</v>
@@ -4078,7 +4087,7 @@
         <v>68</v>
       </c>
       <c r="C72" s="4">
-        <v>470</v>
+        <v>618</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -4095,7 +4104,7 @@
         <v>457</v>
       </c>
       <c r="C73" s="6">
-        <v>1000</v>
+        <v>1147</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>776</v>
@@ -4129,7 +4138,7 @@
         <v>70</v>
       </c>
       <c r="C75" s="6">
-        <v>416</v>
+        <v>664</v>
       </c>
       <c r="D75" s="5">
         <v>5</v>
@@ -4146,7 +4155,7 @@
         <v>461</v>
       </c>
       <c r="C76" s="4">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>776</v>
@@ -4180,7 +4189,7 @@
         <v>465</v>
       </c>
       <c r="C78" s="4">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>776</v>
@@ -4197,7 +4206,7 @@
         <v>72</v>
       </c>
       <c r="C79" s="6">
-        <v>355</v>
+        <v>526</v>
       </c>
       <c r="D79" s="5">
         <v>2</v>
@@ -4214,7 +4223,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>3500</v>
+        <v>4337</v>
       </c>
       <c r="D80" s="3">
         <v>4</v>
@@ -4231,7 +4240,7 @@
         <v>467</v>
       </c>
       <c r="C81" s="6">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>776</v>
@@ -4248,7 +4257,7 @@
         <v>469</v>
       </c>
       <c r="C82" s="4">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>776</v>
@@ -4282,7 +4291,7 @@
         <v>76</v>
       </c>
       <c r="C84" s="4">
-        <v>1283</v>
+        <v>1421</v>
       </c>
       <c r="D84" s="3">
         <v>3</v>
@@ -4299,7 +4308,7 @@
         <v>78</v>
       </c>
       <c r="C85" s="6">
-        <v>2000</v>
+        <v>2402</v>
       </c>
       <c r="D85" s="5">
         <v>1</v>
@@ -4316,7 +4325,7 @@
         <v>80</v>
       </c>
       <c r="C86" s="4">
-        <v>2345</v>
+        <v>3190</v>
       </c>
       <c r="D86" s="3">
         <v>3</v>
@@ -4333,7 +4342,7 @@
         <v>82</v>
       </c>
       <c r="C87" s="6">
-        <v>302</v>
+        <v>612</v>
       </c>
       <c r="D87" s="5">
         <v>3</v>
@@ -4367,7 +4376,7 @@
         <v>475</v>
       </c>
       <c r="C89" s="6">
-        <v>0</v>
+        <v>1641</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>776</v>
@@ -4384,7 +4393,7 @@
         <v>477</v>
       </c>
       <c r="C90" s="4">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>776</v>
@@ -4401,7 +4410,7 @@
         <v>479</v>
       </c>
       <c r="C91" s="6">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>776</v>
@@ -4418,7 +4427,7 @@
         <v>84</v>
       </c>
       <c r="C92" s="4">
-        <v>1013</v>
+        <v>1437</v>
       </c>
       <c r="D92" s="3">
         <v>4</v>
@@ -4435,7 +4444,7 @@
         <v>481</v>
       </c>
       <c r="C93" s="6">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>776</v>
@@ -4452,7 +4461,7 @@
         <v>483</v>
       </c>
       <c r="C94" s="4">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>776</v>
@@ -4469,7 +4478,7 @@
         <v>485</v>
       </c>
       <c r="C95" s="6">
-        <v>0</v>
+        <v>537</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>776</v>
@@ -4486,7 +4495,7 @@
         <v>487</v>
       </c>
       <c r="C96" s="4">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>776</v>
@@ -4520,7 +4529,7 @@
         <v>491</v>
       </c>
       <c r="C98" s="4">
-        <v>1000</v>
+        <v>1288</v>
       </c>
       <c r="D98" s="3">
         <v>3</v>
@@ -4537,7 +4546,7 @@
         <v>493</v>
       </c>
       <c r="C99" s="6">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>776</v>
@@ -4554,7 +4563,7 @@
         <v>86</v>
       </c>
       <c r="C100" s="4">
-        <v>898</v>
+        <v>1472</v>
       </c>
       <c r="D100" s="3">
         <v>4</v>
@@ -4571,7 +4580,7 @@
         <v>87</v>
       </c>
       <c r="C101" s="6">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>776</v>
@@ -4588,7 +4597,7 @@
         <v>495</v>
       </c>
       <c r="C102" s="4">
-        <v>0</v>
+        <v>2328</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>776</v>
@@ -4605,7 +4614,7 @@
         <v>497</v>
       </c>
       <c r="C103" s="6">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>776</v>
@@ -4622,7 +4631,7 @@
         <v>89</v>
       </c>
       <c r="C104" s="4">
-        <v>601</v>
+        <v>1383</v>
       </c>
       <c r="D104" s="3">
         <v>2</v>
@@ -4639,7 +4648,7 @@
         <v>91</v>
       </c>
       <c r="C105" s="6">
-        <v>251</v>
+        <v>906</v>
       </c>
       <c r="D105" s="5">
         <v>5</v>
@@ -4673,7 +4682,7 @@
         <v>501</v>
       </c>
       <c r="C107" s="6">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>776</v>
@@ -4690,7 +4699,7 @@
         <v>503</v>
       </c>
       <c r="C108" s="4">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>776</v>
@@ -4707,7 +4716,7 @@
         <v>505</v>
       </c>
       <c r="C109" s="6">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>776</v>
@@ -4724,7 +4733,7 @@
         <v>507</v>
       </c>
       <c r="C110" s="4">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>776</v>
@@ -4741,7 +4750,7 @@
         <v>93</v>
       </c>
       <c r="C111" s="6">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="D111" s="5">
         <v>2</v>
@@ -4758,7 +4767,7 @@
         <v>95</v>
       </c>
       <c r="C112" s="4">
-        <v>893</v>
+        <v>1506</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -4775,7 +4784,7 @@
         <v>509</v>
       </c>
       <c r="C113" s="6">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>776</v>
@@ -4792,7 +4801,7 @@
         <v>511</v>
       </c>
       <c r="C114" s="4">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>776</v>
@@ -4809,7 +4818,7 @@
         <v>513</v>
       </c>
       <c r="C115" s="6">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>776</v>
@@ -4826,7 +4835,7 @@
         <v>515</v>
       </c>
       <c r="C116" s="4">
-        <v>1000</v>
+        <v>1169</v>
       </c>
       <c r="D116" s="3">
         <v>2</v>
@@ -4843,7 +4852,7 @@
         <v>97</v>
       </c>
       <c r="C117" s="6">
-        <v>266</v>
+        <v>571</v>
       </c>
       <c r="D117" s="5">
         <v>4</v>
@@ -4860,7 +4869,7 @@
         <v>517</v>
       </c>
       <c r="C118" s="4">
-        <v>0</v>
+        <v>2533</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>776</v>
@@ -4877,7 +4886,7 @@
         <v>99</v>
       </c>
       <c r="C119" s="6">
-        <v>948</v>
+        <v>1456</v>
       </c>
       <c r="D119" s="5">
         <v>6</v>
@@ -4894,7 +4903,7 @@
         <v>101</v>
       </c>
       <c r="C120" s="4">
-        <v>559</v>
+        <v>843</v>
       </c>
       <c r="D120" s="3">
         <v>4</v>
@@ -4911,7 +4920,7 @@
         <v>519</v>
       </c>
       <c r="C121" s="6">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>776</v>
@@ -4928,7 +4937,7 @@
         <v>103</v>
       </c>
       <c r="C122" s="4">
-        <v>1000</v>
+        <v>4877</v>
       </c>
       <c r="D122" s="3">
         <v>5</v>
@@ -4945,7 +4954,7 @@
         <v>105</v>
       </c>
       <c r="C123" s="6">
-        <v>542</v>
+        <v>895</v>
       </c>
       <c r="D123" s="5">
         <v>5</v>
@@ -4962,7 +4971,7 @@
         <v>521</v>
       </c>
       <c r="C124" s="4">
-        <v>278</v>
+        <v>629</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>776</v>
@@ -4979,7 +4988,7 @@
         <v>523</v>
       </c>
       <c r="C125" s="6">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>776</v>
@@ -4996,7 +5005,7 @@
         <v>525</v>
       </c>
       <c r="C126" s="4">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>776</v>
@@ -5013,7 +5022,7 @@
         <v>107</v>
       </c>
       <c r="C127" s="6">
-        <v>451</v>
+        <v>758</v>
       </c>
       <c r="D127" s="5">
         <v>3</v>
@@ -5030,7 +5039,7 @@
         <v>527</v>
       </c>
       <c r="C128" s="4">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>776</v>
@@ -5047,7 +5056,7 @@
         <v>109</v>
       </c>
       <c r="C129" s="6">
-        <v>1550</v>
+        <v>1870</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>778</v>
@@ -5064,7 +5073,7 @@
         <v>111</v>
       </c>
       <c r="C130" s="4">
-        <v>608</v>
+        <v>850</v>
       </c>
       <c r="D130" s="3">
         <v>1</v>
@@ -5081,7 +5090,7 @@
         <v>529</v>
       </c>
       <c r="C131" s="6">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>776</v>
@@ -5098,7 +5107,7 @@
         <v>113</v>
       </c>
       <c r="C132" s="4">
-        <v>979</v>
+        <v>1828</v>
       </c>
       <c r="D132" s="3">
         <v>2</v>
@@ -5115,7 +5124,7 @@
         <v>531</v>
       </c>
       <c r="C133" s="6">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>776</v>
@@ -5132,7 +5141,7 @@
         <v>533</v>
       </c>
       <c r="C134" s="4">
-        <v>776</v>
+        <v>992</v>
       </c>
       <c r="D134" s="3">
         <v>3</v>
@@ -5149,7 +5158,7 @@
         <v>535</v>
       </c>
       <c r="C135" s="6">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>776</v>
@@ -5166,7 +5175,7 @@
         <v>537</v>
       </c>
       <c r="C136" s="4">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>776</v>
@@ -5183,7 +5192,7 @@
         <v>539</v>
       </c>
       <c r="C137" s="6">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>776</v>
@@ -5200,7 +5209,7 @@
         <v>541</v>
       </c>
       <c r="C138" s="4">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>776</v>
@@ -5217,7 +5226,7 @@
         <v>115</v>
       </c>
       <c r="C139" s="6">
-        <v>518</v>
+        <v>1025</v>
       </c>
       <c r="D139" s="5">
         <v>5</v>
@@ -5234,7 +5243,7 @@
         <v>117</v>
       </c>
       <c r="C140" s="4">
-        <v>609</v>
+        <v>873</v>
       </c>
       <c r="D140" s="3">
         <v>1</v>
@@ -5251,7 +5260,7 @@
         <v>543</v>
       </c>
       <c r="C141" s="6">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>776</v>
@@ -5268,7 +5277,7 @@
         <v>119</v>
       </c>
       <c r="C142" s="4">
-        <v>1218</v>
+        <v>1457</v>
       </c>
       <c r="D142" s="3">
         <v>2</v>
@@ -5285,7 +5294,7 @@
         <v>121</v>
       </c>
       <c r="C143" s="6">
-        <v>1000</v>
+        <v>1203</v>
       </c>
       <c r="D143" s="5">
         <v>3</v>
@@ -5302,7 +5311,7 @@
         <v>545</v>
       </c>
       <c r="C144" s="4">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>776</v>
@@ -5319,7 +5328,7 @@
         <v>123</v>
       </c>
       <c r="C145" s="6">
-        <v>701</v>
+        <v>868</v>
       </c>
       <c r="D145" s="5">
         <v>6</v>
@@ -5336,7 +5345,7 @@
         <v>547</v>
       </c>
       <c r="C146" s="4">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>776</v>
@@ -5370,7 +5379,7 @@
         <v>125</v>
       </c>
       <c r="C148" s="4">
-        <v>1000</v>
+        <v>1308</v>
       </c>
       <c r="D148" s="3">
         <v>5</v>
@@ -5387,7 +5396,7 @@
         <v>551</v>
       </c>
       <c r="C149" s="6">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>776</v>
@@ -5404,7 +5413,7 @@
         <v>553</v>
       </c>
       <c r="C150" s="4">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>776</v>
@@ -5438,7 +5447,7 @@
         <v>557</v>
       </c>
       <c r="C152" s="4">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>776</v>
@@ -5455,7 +5464,7 @@
         <v>559</v>
       </c>
       <c r="C153" s="6">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>776</v>
@@ -5506,7 +5515,7 @@
         <v>561</v>
       </c>
       <c r="C156" s="4">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>776</v>
@@ -5523,7 +5532,7 @@
         <v>563</v>
       </c>
       <c r="C157" s="6">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>776</v>
@@ -5540,7 +5549,7 @@
         <v>131</v>
       </c>
       <c r="C158" s="4">
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="D158" s="3">
         <v>6</v>
@@ -5557,7 +5566,7 @@
         <v>565</v>
       </c>
       <c r="C159" s="6">
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>776</v>
@@ -5574,7 +5583,7 @@
         <v>133</v>
       </c>
       <c r="C160" s="4">
-        <v>1165</v>
+        <v>1831</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -5591,7 +5600,7 @@
         <v>135</v>
       </c>
       <c r="C161" s="6">
-        <v>196</v>
+        <v>696</v>
       </c>
       <c r="D161" s="5">
         <v>4</v>
@@ -5625,7 +5634,7 @@
         <v>569</v>
       </c>
       <c r="C163" s="6">
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>776</v>
@@ -5642,7 +5651,7 @@
         <v>137</v>
       </c>
       <c r="C164" s="4">
-        <v>2757</v>
+        <v>3019</v>
       </c>
       <c r="D164" s="3">
         <v>1</v>
@@ -5659,7 +5668,7 @@
         <v>571</v>
       </c>
       <c r="C165" s="6">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>776</v>
@@ -5676,7 +5685,7 @@
         <v>573</v>
       </c>
       <c r="C166" s="4">
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>776</v>
@@ -5693,7 +5702,7 @@
         <v>139</v>
       </c>
       <c r="C167" s="6">
-        <v>603</v>
+        <v>1022</v>
       </c>
       <c r="D167" s="5">
         <v>4</v>
@@ -5710,7 +5719,7 @@
         <v>141</v>
       </c>
       <c r="C168" s="4">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -5727,7 +5736,7 @@
         <v>575</v>
       </c>
       <c r="C169" s="6">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>776</v>
@@ -5744,7 +5753,7 @@
         <v>577</v>
       </c>
       <c r="C170" s="4">
-        <v>855</v>
+        <v>1245</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>776</v>
@@ -5778,7 +5787,7 @@
         <v>145</v>
       </c>
       <c r="C172" s="4">
-        <v>739</v>
+        <v>1182</v>
       </c>
       <c r="D172" s="3">
         <v>5</v>
@@ -5795,7 +5804,7 @@
         <v>147</v>
       </c>
       <c r="C173" s="6">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="D173" s="5">
         <v>4</v>
@@ -5812,7 +5821,7 @@
         <v>579</v>
       </c>
       <c r="C174" s="4">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>776</v>
@@ -5829,7 +5838,7 @@
         <v>149</v>
       </c>
       <c r="C175" s="6">
-        <v>1008</v>
+        <v>1354</v>
       </c>
       <c r="D175" s="5">
         <v>5</v>
@@ -5863,7 +5872,7 @@
         <v>581</v>
       </c>
       <c r="C177" s="6">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>776</v>
@@ -5880,7 +5889,7 @@
         <v>583</v>
       </c>
       <c r="C178" s="4">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>776</v>
@@ -5897,7 +5906,7 @@
         <v>585</v>
       </c>
       <c r="C179" s="6">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>776</v>
@@ -5914,7 +5923,7 @@
         <v>587</v>
       </c>
       <c r="C180" s="4">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>776</v>
@@ -5931,7 +5940,7 @@
         <v>153</v>
       </c>
       <c r="C181" s="6">
-        <v>286</v>
+        <v>601</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>778</v>
@@ -5948,7 +5957,7 @@
         <v>155</v>
       </c>
       <c r="C182" s="4">
-        <v>307</v>
+        <v>574</v>
       </c>
       <c r="D182" s="3">
         <v>6</v>
@@ -5965,7 +5974,7 @@
         <v>589</v>
       </c>
       <c r="C183" s="6">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>776</v>
@@ -5982,7 +5991,7 @@
         <v>591</v>
       </c>
       <c r="C184" s="4">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>776</v>
@@ -5999,7 +6008,7 @@
         <v>593</v>
       </c>
       <c r="C185" s="6">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>776</v>
@@ -6016,7 +6025,7 @@
         <v>157</v>
       </c>
       <c r="C186" s="4">
-        <v>110</v>
+        <v>1475</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>778</v>
@@ -6033,7 +6042,7 @@
         <v>159</v>
       </c>
       <c r="C187" s="6">
-        <v>10</v>
+        <v>310</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>778</v>
@@ -6050,7 +6059,7 @@
         <v>161</v>
       </c>
       <c r="C188" s="4">
-        <v>868</v>
+        <v>1991</v>
       </c>
       <c r="D188" s="3">
         <v>3</v>
@@ -6067,7 +6076,7 @@
         <v>595</v>
       </c>
       <c r="C189" s="6">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>776</v>
@@ -6084,7 +6093,7 @@
         <v>163</v>
       </c>
       <c r="C190" s="4">
-        <v>1484</v>
+        <v>2114</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6101,7 +6110,7 @@
         <v>597</v>
       </c>
       <c r="C191" s="6">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>776</v>
@@ -6118,7 +6127,7 @@
         <v>599</v>
       </c>
       <c r="C192" s="4">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="D192" s="3">
         <v>3</v>
@@ -6135,7 +6144,7 @@
         <v>165</v>
       </c>
       <c r="C193" s="6">
-        <v>707</v>
+        <v>916</v>
       </c>
       <c r="D193" s="5">
         <v>6</v>
@@ -6152,7 +6161,7 @@
         <v>167</v>
       </c>
       <c r="C194" s="4">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="D194" s="3">
         <v>3</v>
@@ -6169,7 +6178,7 @@
         <v>169</v>
       </c>
       <c r="C195" s="6">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="D195" s="5">
         <v>1</v>
@@ -6186,7 +6195,7 @@
         <v>171</v>
       </c>
       <c r="C196" s="4">
-        <v>2007</v>
+        <v>2304</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6203,7 +6212,7 @@
         <v>601</v>
       </c>
       <c r="C197" s="6">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>776</v>
@@ -6237,7 +6246,7 @@
         <v>173</v>
       </c>
       <c r="C199" s="6">
-        <v>235</v>
+        <v>486</v>
       </c>
       <c r="D199" s="5">
         <v>3</v>
@@ -6254,7 +6263,7 @@
         <v>605</v>
       </c>
       <c r="C200" s="4">
-        <v>0</v>
+        <v>1201</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>776</v>
@@ -6271,7 +6280,7 @@
         <v>175</v>
       </c>
       <c r="C201" s="6">
-        <v>942</v>
+        <v>1244</v>
       </c>
       <c r="D201" s="5">
         <v>5</v>
@@ -6288,7 +6297,7 @@
         <v>177</v>
       </c>
       <c r="C202" s="4">
-        <v>215</v>
+        <v>607</v>
       </c>
       <c r="D202" s="3">
         <v>2</v>
@@ -6305,7 +6314,7 @@
         <v>179</v>
       </c>
       <c r="C203" s="6">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="D203" s="5">
         <v>1</v>
@@ -6322,7 +6331,7 @@
         <v>181</v>
       </c>
       <c r="C204" s="4">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -6339,7 +6348,7 @@
         <v>607</v>
       </c>
       <c r="C205" s="6">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>776</v>
@@ -6356,7 +6365,7 @@
         <v>609</v>
       </c>
       <c r="C206" s="4">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>776</v>
@@ -6373,7 +6382,7 @@
         <v>611</v>
       </c>
       <c r="C207" s="6">
-        <v>1000</v>
+        <v>1343</v>
       </c>
       <c r="D207" s="5">
         <v>5</v>
@@ -6390,7 +6399,7 @@
         <v>183</v>
       </c>
       <c r="C208" s="4">
-        <v>112</v>
+        <v>385</v>
       </c>
       <c r="D208" s="3">
         <v>5</v>
@@ -6407,7 +6416,7 @@
         <v>185</v>
       </c>
       <c r="C209" s="6">
-        <v>402</v>
+        <v>964</v>
       </c>
       <c r="D209" s="5">
         <v>3</v>
@@ -6424,7 +6433,7 @@
         <v>613</v>
       </c>
       <c r="C210" s="4">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>776</v>
@@ -6441,7 +6450,7 @@
         <v>615</v>
       </c>
       <c r="C211" s="6">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>776</v>
@@ -6458,7 +6467,7 @@
         <v>187</v>
       </c>
       <c r="C212" s="4">
-        <v>54</v>
+        <v>414</v>
       </c>
       <c r="D212" s="3">
         <v>3</v>
@@ -6475,7 +6484,7 @@
         <v>617</v>
       </c>
       <c r="C213" s="6">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>776</v>
@@ -6492,7 +6501,7 @@
         <v>619</v>
       </c>
       <c r="C214" s="4">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>776</v>
@@ -6509,7 +6518,7 @@
         <v>189</v>
       </c>
       <c r="C215" s="6">
-        <v>345</v>
+        <v>652</v>
       </c>
       <c r="D215" s="5">
         <v>5</v>
@@ -6526,7 +6535,7 @@
         <v>621</v>
       </c>
       <c r="C216" s="4">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>776</v>
@@ -6543,7 +6552,7 @@
         <v>623</v>
       </c>
       <c r="C217" s="6">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="D217" s="5" t="s">
         <v>776</v>
@@ -6560,7 +6569,7 @@
         <v>191</v>
       </c>
       <c r="C218" s="4">
-        <v>356</v>
+        <v>869</v>
       </c>
       <c r="D218" s="3">
         <v>3</v>
@@ -6577,7 +6586,7 @@
         <v>193</v>
       </c>
       <c r="C219" s="6">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="D219" s="5">
         <v>5</v>
@@ -6594,7 +6603,7 @@
         <v>195</v>
       </c>
       <c r="C220" s="4">
-        <v>322</v>
+        <v>607</v>
       </c>
       <c r="D220" s="3">
         <v>5</v>
@@ -6611,7 +6620,7 @@
         <v>625</v>
       </c>
       <c r="C221" s="6">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="D221" s="5" t="s">
         <v>776</v>
@@ -6628,7 +6637,7 @@
         <v>627</v>
       </c>
       <c r="C222" s="4">
-        <v>138</v>
+        <v>393</v>
       </c>
       <c r="D222" s="3">
         <v>4</v>
@@ -6645,7 +6654,7 @@
         <v>629</v>
       </c>
       <c r="C223" s="6">
-        <v>1500</v>
+        <v>1806</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>776</v>
@@ -6662,7 +6671,7 @@
         <v>631</v>
       </c>
       <c r="C224" s="4">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>776</v>
@@ -6679,7 +6688,7 @@
         <v>633</v>
       </c>
       <c r="C225" s="6">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>776</v>
@@ -6696,7 +6705,7 @@
         <v>197</v>
       </c>
       <c r="C226" s="4">
-        <v>604</v>
+        <v>786</v>
       </c>
       <c r="D226" s="3">
         <v>3</v>
@@ -6713,7 +6722,7 @@
         <v>199</v>
       </c>
       <c r="C227" s="6">
-        <v>1616</v>
+        <v>1818</v>
       </c>
       <c r="D227" s="5">
         <v>1</v>
@@ -6730,7 +6739,7 @@
         <v>635</v>
       </c>
       <c r="C228" s="4">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>776</v>
@@ -6747,7 +6756,7 @@
         <v>201</v>
       </c>
       <c r="C229" s="6">
-        <v>2052</v>
+        <v>2922</v>
       </c>
       <c r="D229" s="5">
         <v>4</v>
@@ -6764,7 +6773,7 @@
         <v>203</v>
       </c>
       <c r="C230" s="4">
-        <v>1262</v>
+        <v>1560</v>
       </c>
       <c r="D230" s="3">
         <v>2</v>
@@ -6781,7 +6790,7 @@
         <v>637</v>
       </c>
       <c r="C231" s="6">
-        <v>1013</v>
+        <v>1603</v>
       </c>
       <c r="D231" s="5" t="s">
         <v>776</v>
@@ -6798,7 +6807,7 @@
         <v>639</v>
       </c>
       <c r="C232" s="4">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>776</v>
@@ -6815,7 +6824,7 @@
         <v>641</v>
       </c>
       <c r="C233" s="6">
-        <v>500</v>
+        <v>790</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>776</v>
@@ -6832,7 +6841,7 @@
         <v>205</v>
       </c>
       <c r="C234" s="4">
-        <v>800</v>
+        <v>1362</v>
       </c>
       <c r="D234" s="3">
         <v>2</v>
@@ -6849,7 +6858,7 @@
         <v>207</v>
       </c>
       <c r="C235" s="6">
-        <v>198</v>
+        <v>491</v>
       </c>
       <c r="D235" s="5">
         <v>3</v>
@@ -6883,7 +6892,7 @@
         <v>645</v>
       </c>
       <c r="C237" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D237" s="5" t="s">
         <v>776</v>
@@ -6900,7 +6909,7 @@
         <v>209</v>
       </c>
       <c r="C238" s="4">
-        <v>618</v>
+        <v>1066</v>
       </c>
       <c r="D238" s="3">
         <v>1</v>
@@ -6917,7 +6926,7 @@
         <v>647</v>
       </c>
       <c r="C239" s="6">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D239" s="5" t="s">
         <v>776</v>
@@ -6934,7 +6943,7 @@
         <v>649</v>
       </c>
       <c r="C240" s="4">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>776</v>
@@ -6951,7 +6960,7 @@
         <v>651</v>
       </c>
       <c r="C241" s="6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>776</v>
@@ -6968,7 +6977,7 @@
         <v>653</v>
       </c>
       <c r="C242" s="4">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>776</v>
@@ -6985,7 +6994,7 @@
         <v>655</v>
       </c>
       <c r="C243" s="6">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="D243" s="5" t="s">
         <v>776</v>
@@ -7002,7 +7011,7 @@
         <v>211</v>
       </c>
       <c r="C244" s="4">
-        <v>800</v>
+        <v>1041</v>
       </c>
       <c r="D244" s="3">
         <v>5</v>
@@ -7019,7 +7028,7 @@
         <v>213</v>
       </c>
       <c r="C245" s="6">
-        <v>210</v>
+        <v>1048</v>
       </c>
       <c r="D245" s="5">
         <v>6</v>
@@ -7036,7 +7045,7 @@
         <v>657</v>
       </c>
       <c r="C246" s="4">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>776</v>
@@ -7053,7 +7062,7 @@
         <v>215</v>
       </c>
       <c r="C247" s="6">
-        <v>598</v>
+        <v>898</v>
       </c>
       <c r="D247" s="5">
         <v>6</v>
@@ -7070,7 +7079,7 @@
         <v>217</v>
       </c>
       <c r="C248" s="4">
-        <v>199</v>
+        <v>677</v>
       </c>
       <c r="D248" s="3">
         <v>4</v>
@@ -7087,7 +7096,7 @@
         <v>659</v>
       </c>
       <c r="C249" s="6">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>776</v>
@@ -7104,7 +7113,7 @@
         <v>661</v>
       </c>
       <c r="C250" s="4">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>776</v>
@@ -7121,7 +7130,7 @@
         <v>663</v>
       </c>
       <c r="C251" s="6">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="D251" s="5" t="s">
         <v>776</v>
@@ -7138,7 +7147,7 @@
         <v>665</v>
       </c>
       <c r="C252" s="4">
-        <v>1000</v>
+        <v>1183</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>776</v>
@@ -7155,7 +7164,7 @@
         <v>219</v>
       </c>
       <c r="C253" s="6">
-        <v>956</v>
+        <v>1252</v>
       </c>
       <c r="D253" s="5">
         <v>4</v>
@@ -7172,7 +7181,7 @@
         <v>221</v>
       </c>
       <c r="C254" s="4">
-        <v>401</v>
+        <v>494</v>
       </c>
       <c r="D254" s="3">
         <v>2</v>
@@ -7189,7 +7198,7 @@
         <v>667</v>
       </c>
       <c r="C255" s="6">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="D255" s="5" t="s">
         <v>776</v>
@@ -7206,7 +7215,7 @@
         <v>669</v>
       </c>
       <c r="C256" s="4">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>776</v>
@@ -7223,7 +7232,7 @@
         <v>223</v>
       </c>
       <c r="C257" s="6">
-        <v>248</v>
+        <v>546</v>
       </c>
       <c r="D257" s="5">
         <v>4</v>
@@ -7240,7 +7249,7 @@
         <v>225</v>
       </c>
       <c r="C258" s="4">
-        <v>675</v>
+        <v>997</v>
       </c>
       <c r="D258" s="3">
         <v>4</v>
@@ -7257,7 +7266,7 @@
         <v>671</v>
       </c>
       <c r="C259" s="6">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="D259" s="5" t="s">
         <v>776</v>
@@ -7274,7 +7283,7 @@
         <v>227</v>
       </c>
       <c r="C260" s="4">
-        <v>605</v>
+        <v>929</v>
       </c>
       <c r="D260" s="3">
         <v>2</v>
@@ -7291,7 +7300,7 @@
         <v>229</v>
       </c>
       <c r="C261" s="6">
-        <v>442</v>
+        <v>961</v>
       </c>
       <c r="D261" s="5">
         <v>3</v>
@@ -7308,7 +7317,7 @@
         <v>231</v>
       </c>
       <c r="C262" s="4">
-        <v>1079</v>
+        <v>1403</v>
       </c>
       <c r="D262" s="3">
         <v>6</v>
@@ -7325,7 +7334,7 @@
         <v>233</v>
       </c>
       <c r="C263" s="6">
-        <v>458</v>
+        <v>980</v>
       </c>
       <c r="D263" s="5">
         <v>3</v>
@@ -7342,7 +7351,7 @@
         <v>673</v>
       </c>
       <c r="C264" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>776</v>
@@ -7359,7 +7368,7 @@
         <v>235</v>
       </c>
       <c r="C265" s="6">
-        <v>150</v>
+        <v>772</v>
       </c>
       <c r="D265" s="5">
         <v>6</v>
@@ -7376,7 +7385,7 @@
         <v>237</v>
       </c>
       <c r="C266" s="4">
-        <v>470</v>
+        <v>786</v>
       </c>
       <c r="D266" s="3">
         <v>3</v>
@@ -7393,7 +7402,7 @@
         <v>675</v>
       </c>
       <c r="C267" s="6">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="D267" s="5" t="s">
         <v>776</v>
@@ -7427,7 +7436,7 @@
         <v>679</v>
       </c>
       <c r="C269" s="6">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="D269" s="5" t="s">
         <v>776</v>
@@ -7444,7 +7453,7 @@
         <v>681</v>
       </c>
       <c r="C270" s="4">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>776</v>
@@ -7461,7 +7470,7 @@
         <v>239</v>
       </c>
       <c r="C271" s="6">
-        <v>708</v>
+        <v>1365</v>
       </c>
       <c r="D271" s="5">
         <v>2</v>
@@ -7478,7 +7487,7 @@
         <v>241</v>
       </c>
       <c r="C272" s="4">
-        <v>109</v>
+        <v>430</v>
       </c>
       <c r="D272" s="3">
         <v>3</v>
@@ -7495,7 +7504,7 @@
         <v>683</v>
       </c>
       <c r="C273" s="6">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="D273" s="5" t="s">
         <v>776</v>
@@ -7529,7 +7538,7 @@
         <v>245</v>
       </c>
       <c r="C275" s="6">
-        <v>300</v>
+        <v>580</v>
       </c>
       <c r="D275" s="5">
         <v>3</v>
@@ -7546,7 +7555,7 @@
         <v>685</v>
       </c>
       <c r="C276" s="4">
-        <v>0</v>
+        <v>988</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>776</v>
@@ -7563,7 +7572,7 @@
         <v>687</v>
       </c>
       <c r="C277" s="6">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D277" s="5" t="s">
         <v>776</v>
@@ -7597,7 +7606,7 @@
         <v>249</v>
       </c>
       <c r="C279" s="6">
-        <v>1089</v>
+        <v>1544</v>
       </c>
       <c r="D279" s="5">
         <v>2</v>
@@ -7614,7 +7623,7 @@
         <v>689</v>
       </c>
       <c r="C280" s="4">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>776</v>
@@ -7631,7 +7640,7 @@
         <v>251</v>
       </c>
       <c r="C281" s="6">
-        <v>800</v>
+        <v>898</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -7665,7 +7674,7 @@
         <v>253</v>
       </c>
       <c r="C283" s="6">
-        <v>1605</v>
+        <v>1952</v>
       </c>
       <c r="D283" s="5">
         <v>3</v>
@@ -7682,7 +7691,7 @@
         <v>255</v>
       </c>
       <c r="C284" s="4">
-        <v>303</v>
+        <v>756</v>
       </c>
       <c r="D284" s="3">
         <v>1</v>
@@ -7699,7 +7708,7 @@
         <v>693</v>
       </c>
       <c r="C285" s="6">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="D285" s="5" t="s">
         <v>776</v>
@@ -7716,7 +7725,7 @@
         <v>257</v>
       </c>
       <c r="C286" s="4">
-        <v>754</v>
+        <v>1411</v>
       </c>
       <c r="D286" s="3">
         <v>4</v>
@@ -7733,7 +7742,7 @@
         <v>259</v>
       </c>
       <c r="C287" s="6">
-        <v>148</v>
+        <v>383</v>
       </c>
       <c r="D287" s="5">
         <v>2</v>
@@ -7750,7 +7759,7 @@
         <v>695</v>
       </c>
       <c r="C288" s="4">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>776</v>
@@ -7784,7 +7793,7 @@
         <v>699</v>
       </c>
       <c r="C290" s="4">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>776</v>
@@ -7801,7 +7810,7 @@
         <v>701</v>
       </c>
       <c r="C291" s="6">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="D291" s="5" t="s">
         <v>776</v>
@@ -7852,7 +7861,7 @@
         <v>261</v>
       </c>
       <c r="C294" s="4">
-        <v>765</v>
+        <v>1209</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -7869,7 +7878,7 @@
         <v>263</v>
       </c>
       <c r="C295" s="6">
-        <v>811</v>
+        <v>1096</v>
       </c>
       <c r="D295" s="5">
         <v>1</v>
@@ -7886,7 +7895,7 @@
         <v>707</v>
       </c>
       <c r="C296" s="4">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>776</v>
@@ -7903,7 +7912,7 @@
         <v>265</v>
       </c>
       <c r="C297" s="6">
-        <v>717</v>
+        <v>1557</v>
       </c>
       <c r="D297" s="5">
         <v>1</v>
@@ -7920,7 +7929,7 @@
         <v>709</v>
       </c>
       <c r="C298" s="4">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>776</v>
@@ -7954,7 +7963,7 @@
         <v>269</v>
       </c>
       <c r="C300" s="4">
-        <v>31</v>
+        <v>627</v>
       </c>
       <c r="D300" s="3">
         <v>6</v>
@@ -7971,7 +7980,7 @@
         <v>711</v>
       </c>
       <c r="C301" s="6">
-        <v>1000</v>
+        <v>1123</v>
       </c>
       <c r="D301" s="5">
         <v>2</v>
@@ -7988,7 +7997,7 @@
         <v>271</v>
       </c>
       <c r="C302" s="4">
-        <v>649</v>
+        <v>788</v>
       </c>
       <c r="D302" s="3">
         <v>2</v>
@@ -8005,7 +8014,7 @@
         <v>713</v>
       </c>
       <c r="C303" s="6">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D303" s="5" t="s">
         <v>776</v>
@@ -8022,7 +8031,7 @@
         <v>273</v>
       </c>
       <c r="C304" s="4">
-        <v>200</v>
+        <v>653</v>
       </c>
       <c r="D304" s="3">
         <v>6</v>
@@ -8039,7 +8048,7 @@
         <v>275</v>
       </c>
       <c r="C305" s="6">
-        <v>280</v>
+        <v>502</v>
       </c>
       <c r="D305" s="5">
         <v>2</v>
@@ -8056,7 +8065,7 @@
         <v>715</v>
       </c>
       <c r="C306" s="4">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="D306" s="3" t="s">
         <v>776</v>
@@ -8073,7 +8082,7 @@
         <v>277</v>
       </c>
       <c r="C307" s="6">
-        <v>2000</v>
+        <v>2894</v>
       </c>
       <c r="D307" s="5">
         <v>5</v>
@@ -8090,7 +8099,7 @@
         <v>279</v>
       </c>
       <c r="C308" s="4">
-        <v>389</v>
+        <v>638</v>
       </c>
       <c r="D308" s="3">
         <v>6</v>
@@ -8107,7 +8116,7 @@
         <v>717</v>
       </c>
       <c r="C309" s="6">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="D309" s="5" t="s">
         <v>776</v>
@@ -8124,7 +8133,7 @@
         <v>281</v>
       </c>
       <c r="C310" s="4">
-        <v>5</v>
+        <v>269</v>
       </c>
       <c r="D310" s="3">
         <v>2</v>
@@ -8141,7 +8150,7 @@
         <v>283</v>
       </c>
       <c r="C311" s="6">
-        <v>503</v>
+        <v>872</v>
       </c>
       <c r="D311" s="5">
         <v>2</v>
@@ -8158,7 +8167,7 @@
         <v>285</v>
       </c>
       <c r="C312" s="4">
-        <v>987</v>
+        <v>1521</v>
       </c>
       <c r="D312" s="3">
         <v>5</v>
@@ -8175,7 +8184,7 @@
         <v>719</v>
       </c>
       <c r="C313" s="6">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="D313" s="5" t="s">
         <v>776</v>
@@ -8192,7 +8201,7 @@
         <v>287</v>
       </c>
       <c r="C314" s="4">
-        <v>600</v>
+        <v>982</v>
       </c>
       <c r="D314" s="3">
         <v>6</v>
@@ -8209,7 +8218,7 @@
         <v>721</v>
       </c>
       <c r="C315" s="6">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="D315" s="5" t="s">
         <v>776</v>
@@ -8226,7 +8235,7 @@
         <v>289</v>
       </c>
       <c r="C316" s="4">
-        <v>812</v>
+        <v>1096</v>
       </c>
       <c r="D316" s="3">
         <v>6</v>
@@ -8243,7 +8252,7 @@
         <v>291</v>
       </c>
       <c r="C317" s="6">
-        <v>1152</v>
+        <v>1249</v>
       </c>
       <c r="D317" s="5">
         <v>6</v>
@@ -8260,7 +8269,7 @@
         <v>293</v>
       </c>
       <c r="C318" s="4">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="D318" s="3">
         <v>1</v>
@@ -8277,7 +8286,7 @@
         <v>295</v>
       </c>
       <c r="C319" s="6">
-        <v>686</v>
+        <v>1035</v>
       </c>
       <c r="D319" s="5">
         <v>5</v>
@@ -8311,7 +8320,7 @@
         <v>723</v>
       </c>
       <c r="C321" s="6">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="D321" s="5" t="s">
         <v>776</v>
@@ -8328,7 +8337,7 @@
         <v>725</v>
       </c>
       <c r="C322" s="4">
-        <v>1500</v>
+        <v>1937</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>776</v>
@@ -8345,7 +8354,7 @@
         <v>727</v>
       </c>
       <c r="C323" s="6">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="D323" s="5" t="s">
         <v>776</v>
@@ -8362,7 +8371,7 @@
         <v>729</v>
       </c>
       <c r="C324" s="4">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="D324" s="3" t="s">
         <v>776</v>
@@ -8379,7 +8388,7 @@
         <v>299</v>
       </c>
       <c r="C325" s="6">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="D325" s="5">
         <v>3</v>
@@ -8396,7 +8405,7 @@
         <v>731</v>
       </c>
       <c r="C326" s="4">
-        <v>190</v>
+        <v>695</v>
       </c>
       <c r="D326" s="3">
         <v>4</v>
@@ -8413,7 +8422,7 @@
         <v>301</v>
       </c>
       <c r="C327" s="6">
-        <v>1694</v>
+        <v>1982</v>
       </c>
       <c r="D327" s="5">
         <v>4</v>
@@ -8430,7 +8439,7 @@
         <v>733</v>
       </c>
       <c r="C328" s="4">
-        <v>0</v>
+        <v>1273</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>776</v>
@@ -8447,7 +8456,7 @@
         <v>303</v>
       </c>
       <c r="C329" s="6">
-        <v>610</v>
+        <v>983</v>
       </c>
       <c r="D329" s="5">
         <v>4</v>
@@ -8464,7 +8473,7 @@
         <v>305</v>
       </c>
       <c r="C330" s="4">
-        <v>385</v>
+        <v>663</v>
       </c>
       <c r="D330" s="3">
         <v>6</v>
@@ -8481,7 +8490,7 @@
         <v>307</v>
       </c>
       <c r="C331" s="6">
-        <v>397</v>
+        <v>871</v>
       </c>
       <c r="D331" s="5">
         <v>2</v>
@@ -8498,7 +8507,7 @@
         <v>309</v>
       </c>
       <c r="C332" s="4">
-        <v>1500</v>
+        <v>2063</v>
       </c>
       <c r="D332" s="3">
         <v>3</v>
@@ -8515,7 +8524,7 @@
         <v>735</v>
       </c>
       <c r="C333" s="6">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="D333" s="5" t="s">
         <v>776</v>
@@ -8532,7 +8541,7 @@
         <v>311</v>
       </c>
       <c r="C334" s="4">
-        <v>1099</v>
+        <v>1685</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>778</v>
@@ -8549,7 +8558,7 @@
         <v>313</v>
       </c>
       <c r="C335" s="6">
-        <v>17</v>
+        <v>247</v>
       </c>
       <c r="D335" s="5" t="s">
         <v>778</v>
@@ -8566,7 +8575,7 @@
         <v>315</v>
       </c>
       <c r="C336" s="4">
-        <v>697</v>
+        <v>915</v>
       </c>
       <c r="D336" s="3">
         <v>6</v>
@@ -8600,7 +8609,7 @@
         <v>317</v>
       </c>
       <c r="C338" s="4">
-        <v>6216</v>
+        <v>6366</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>778</v>
@@ -8617,7 +8626,7 @@
         <v>319</v>
       </c>
       <c r="C339" s="6">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="D339" s="5">
         <v>6</v>
@@ -8668,7 +8677,7 @@
         <v>741</v>
       </c>
       <c r="C342" s="4">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="D342" s="3" t="s">
         <v>776</v>
@@ -8685,7 +8694,7 @@
         <v>323</v>
       </c>
       <c r="C343" s="6">
-        <v>148</v>
+        <v>619</v>
       </c>
       <c r="D343" s="5">
         <v>6</v>
@@ -8702,7 +8711,7 @@
         <v>325</v>
       </c>
       <c r="C344" s="4">
-        <v>466</v>
+        <v>1379</v>
       </c>
       <c r="D344" s="3">
         <v>4</v>
@@ -8719,7 +8728,7 @@
         <v>327</v>
       </c>
       <c r="C345" s="6">
-        <v>291</v>
+        <v>621</v>
       </c>
       <c r="D345" s="5">
         <v>4</v>
@@ -8736,7 +8745,7 @@
         <v>329</v>
       </c>
       <c r="C346" s="4">
-        <v>205</v>
+        <v>690</v>
       </c>
       <c r="D346" s="3">
         <v>5</v>
@@ -8753,7 +8762,7 @@
         <v>331</v>
       </c>
       <c r="C347" s="6">
-        <v>487</v>
+        <v>1087</v>
       </c>
       <c r="D347" s="5">
         <v>3</v>
@@ -8770,7 +8779,7 @@
         <v>743</v>
       </c>
       <c r="C348" s="4">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>776</v>
@@ -8787,7 +8796,7 @@
         <v>333</v>
       </c>
       <c r="C349" s="6">
-        <v>1612</v>
+        <v>2009</v>
       </c>
       <c r="D349" s="5">
         <v>5</v>
@@ -8804,7 +8813,7 @@
         <v>745</v>
       </c>
       <c r="C350" s="4">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>776</v>
@@ -8821,7 +8830,7 @@
         <v>747</v>
       </c>
       <c r="C351" s="6">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="D351" s="5" t="s">
         <v>776</v>
@@ -8838,7 +8847,7 @@
         <v>335</v>
       </c>
       <c r="C352" s="4">
-        <v>3284</v>
+        <v>3756</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>
@@ -8872,7 +8881,7 @@
         <v>339</v>
       </c>
       <c r="C354" s="4">
-        <v>282</v>
+        <v>651</v>
       </c>
       <c r="D354" s="3">
         <v>2</v>
@@ -8889,7 +8898,7 @@
         <v>749</v>
       </c>
       <c r="C355" s="6">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="D355" s="5" t="s">
         <v>776</v>
@@ -8906,7 +8915,7 @@
         <v>341</v>
       </c>
       <c r="C356" s="4">
-        <v>147</v>
+        <v>284</v>
       </c>
       <c r="D356" s="3">
         <v>6</v>
@@ -8923,7 +8932,7 @@
         <v>343</v>
       </c>
       <c r="C357" s="6">
-        <v>605</v>
+        <v>1013</v>
       </c>
       <c r="D357" s="5">
         <v>2</v>
@@ -8940,7 +8949,7 @@
         <v>345</v>
       </c>
       <c r="C358" s="4">
-        <v>322</v>
+        <v>1016</v>
       </c>
       <c r="D358" s="3">
         <v>6</v>
@@ -8957,7 +8966,7 @@
         <v>347</v>
       </c>
       <c r="C359" s="6">
-        <v>320</v>
+        <v>624</v>
       </c>
       <c r="D359" s="5" t="s">
         <v>778</v>
@@ -8974,7 +8983,7 @@
         <v>751</v>
       </c>
       <c r="C360" s="4">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>776</v>
@@ -8991,7 +9000,7 @@
         <v>753</v>
       </c>
       <c r="C361" s="6">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D361" s="5" t="s">
         <v>776</v>
@@ -9008,7 +9017,7 @@
         <v>349</v>
       </c>
       <c r="C362" s="4">
-        <v>624</v>
+        <v>930</v>
       </c>
       <c r="D362" s="3">
         <v>4</v>
@@ -9025,7 +9034,7 @@
         <v>351</v>
       </c>
       <c r="C363" s="6">
-        <v>185</v>
+        <v>507</v>
       </c>
       <c r="D363" s="5">
         <v>3</v>
@@ -9042,7 +9051,7 @@
         <v>353</v>
       </c>
       <c r="C364" s="4">
-        <v>700</v>
+        <v>984</v>
       </c>
       <c r="D364" s="3">
         <v>4</v>
@@ -9059,7 +9068,7 @@
         <v>755</v>
       </c>
       <c r="C365" s="6">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="D365" s="5" t="s">
         <v>776</v>
@@ -9076,7 +9085,7 @@
         <v>757</v>
       </c>
       <c r="C366" s="4">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>776</v>
@@ -9093,7 +9102,7 @@
         <v>355</v>
       </c>
       <c r="C367" s="6">
-        <v>603</v>
+        <v>1266</v>
       </c>
       <c r="D367" s="5">
         <v>1</v>
@@ -9110,7 +9119,7 @@
         <v>357</v>
       </c>
       <c r="C368" s="4">
-        <v>66</v>
+        <v>991</v>
       </c>
       <c r="D368" s="3">
         <v>6</v>
@@ -9127,7 +9136,7 @@
         <v>359</v>
       </c>
       <c r="C369" s="6">
-        <v>113</v>
+        <v>410</v>
       </c>
       <c r="D369" s="5">
         <v>3</v>
@@ -9144,7 +9153,7 @@
         <v>361</v>
       </c>
       <c r="C370" s="4">
-        <v>159</v>
+        <v>538</v>
       </c>
       <c r="D370" s="3">
         <v>6</v>
@@ -9161,7 +9170,7 @@
         <v>759</v>
       </c>
       <c r="C371" s="6">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D371" s="5" t="s">
         <v>776</v>
@@ -9178,7 +9187,7 @@
         <v>363</v>
       </c>
       <c r="C372" s="4">
-        <v>1054</v>
+        <v>1663</v>
       </c>
       <c r="D372" s="3">
         <v>1</v>
@@ -9195,7 +9204,7 @@
         <v>365</v>
       </c>
       <c r="C373" s="6">
-        <v>90</v>
+        <v>395</v>
       </c>
       <c r="D373" s="5" t="s">
         <v>778</v>
@@ -9212,7 +9221,7 @@
         <v>761</v>
       </c>
       <c r="C374" s="4">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>776</v>
@@ -9229,7 +9238,7 @@
         <v>367</v>
       </c>
       <c r="C375" s="6">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="D375" s="5">
         <v>5</v>
@@ -9246,7 +9255,7 @@
         <v>763</v>
       </c>
       <c r="C376" s="4">
-        <v>550</v>
+        <v>733</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>776</v>
@@ -9263,7 +9272,7 @@
         <v>765</v>
       </c>
       <c r="C377" s="6">
-        <v>1878</v>
+        <v>2033</v>
       </c>
       <c r="D377" s="5" t="s">
         <v>776</v>
@@ -9280,7 +9289,7 @@
         <v>369</v>
       </c>
       <c r="C378" s="4">
-        <v>749</v>
+        <v>1322</v>
       </c>
       <c r="D378" s="3">
         <v>2</v>
@@ -9297,7 +9306,7 @@
         <v>767</v>
       </c>
       <c r="C379" s="6">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="D379" s="5" t="s">
         <v>776</v>
@@ -9314,7 +9323,7 @@
         <v>371</v>
       </c>
       <c r="C380" s="4">
-        <v>2013</v>
+        <v>2413</v>
       </c>
       <c r="D380" s="3">
         <v>1</v>
@@ -9331,7 +9340,7 @@
         <v>769</v>
       </c>
       <c r="C381" s="6">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="D381" s="5" t="s">
         <v>776</v>
@@ -9348,7 +9357,7 @@
         <v>373</v>
       </c>
       <c r="C382" s="4">
-        <v>710</v>
+        <v>1200</v>
       </c>
       <c r="D382" s="3">
         <v>5</v>
@@ -9365,7 +9374,7 @@
         <v>375</v>
       </c>
       <c r="C383" s="6">
-        <v>249</v>
+        <v>454</v>
       </c>
       <c r="D383" s="5">
         <v>4</v>
@@ -9382,7 +9391,7 @@
         <v>771</v>
       </c>
       <c r="C384" s="4">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>776</v>
@@ -9416,7 +9425,7 @@
         <v>775</v>
       </c>
       <c r="C386" s="4">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>776</v>
@@ -9433,7 +9442,7 @@
         <v>377</v>
       </c>
       <c r="C387" s="6">
-        <v>505</v>
+        <v>776</v>
       </c>
       <c r="D387" s="5">
         <v>3</v>
@@ -9467,7 +9476,7 @@
         <v>786</v>
       </c>
       <c r="C389">
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="D389" t="s">
         <v>776</v>
@@ -9498,10 +9507,10 @@
         <v>789</v>
       </c>
       <c r="B391" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C391">
-        <v>1000</v>
+        <v>532</v>
       </c>
       <c r="D391" t="s">
         <v>776</v>
@@ -9515,7 +9524,7 @@
         <v>790</v>
       </c>
       <c r="B392" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C392">
         <v>1000</v>
@@ -9532,10 +9541,10 @@
         <v>791</v>
       </c>
       <c r="B393" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C393">
-        <v>1000</v>
+        <v>648</v>
       </c>
       <c r="D393" t="s">
         <v>776</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01A5821-7462-4AF6-84D5-A9532321C84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3910ACF8-37C1-4C18-8B35-92A634B30764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6">
-        <v>2778</v>
+        <v>2378</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -3917,7 +3917,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="4">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="D62" s="3">
         <v>3</v>
@@ -3985,7 +3985,7 @@
         <v>64</v>
       </c>
       <c r="C66" s="4">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="D66" s="3">
         <v>3</v>
@@ -4767,7 +4767,7 @@
         <v>95</v>
       </c>
       <c r="C112" s="4">
-        <v>1506</v>
+        <v>951</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -4886,7 +4886,7 @@
         <v>99</v>
       </c>
       <c r="C119" s="6">
-        <v>1456</v>
+        <v>956</v>
       </c>
       <c r="D119" s="5">
         <v>6</v>
@@ -5141,7 +5141,7 @@
         <v>533</v>
       </c>
       <c r="C134" s="4">
-        <v>992</v>
+        <v>792</v>
       </c>
       <c r="D134" s="3">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>115</v>
       </c>
       <c r="C139" s="6">
-        <v>1025</v>
+        <v>825</v>
       </c>
       <c r="D139" s="5">
         <v>5</v>
@@ -5379,7 +5379,7 @@
         <v>125</v>
       </c>
       <c r="C148" s="4">
-        <v>1308</v>
+        <v>808</v>
       </c>
       <c r="D148" s="3">
         <v>5</v>
@@ -5583,7 +5583,7 @@
         <v>133</v>
       </c>
       <c r="C160" s="4">
-        <v>1831</v>
+        <v>1596</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -5787,7 +5787,7 @@
         <v>145</v>
       </c>
       <c r="C172" s="4">
-        <v>1182</v>
+        <v>982</v>
       </c>
       <c r="D172" s="3">
         <v>5</v>
@@ -6093,7 +6093,7 @@
         <v>163</v>
       </c>
       <c r="C190" s="4">
-        <v>2114</v>
+        <v>1614</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6161,7 +6161,7 @@
         <v>167</v>
       </c>
       <c r="C194" s="4">
-        <v>375</v>
+        <v>175</v>
       </c>
       <c r="D194" s="3">
         <v>3</v>
@@ -6280,7 +6280,7 @@
         <v>175</v>
       </c>
       <c r="C201" s="6">
-        <v>1244</v>
+        <v>994</v>
       </c>
       <c r="D201" s="5">
         <v>5</v>
@@ -6331,7 +6331,7 @@
         <v>181</v>
       </c>
       <c r="C204" s="4">
-        <v>268</v>
+        <v>6</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -7011,7 +7011,7 @@
         <v>211</v>
       </c>
       <c r="C244" s="4">
-        <v>1041</v>
+        <v>791</v>
       </c>
       <c r="D244" s="3">
         <v>5</v>
@@ -7334,7 +7334,7 @@
         <v>233</v>
       </c>
       <c r="C263" s="6">
-        <v>980</v>
+        <v>780</v>
       </c>
       <c r="D263" s="5">
         <v>3</v>
@@ -7861,7 +7861,7 @@
         <v>261</v>
       </c>
       <c r="C294" s="4">
-        <v>1209</v>
+        <v>1009</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -8082,7 +8082,7 @@
         <v>277</v>
       </c>
       <c r="C307" s="6">
-        <v>2894</v>
+        <v>2694</v>
       </c>
       <c r="D307" s="5">
         <v>5</v>
@@ -8847,7 +8847,7 @@
         <v>335</v>
       </c>
       <c r="C352" s="4">
-        <v>3756</v>
+        <v>2996</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3910ACF8-37C1-4C18-8B35-92A634B30764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05482FB6-94CB-4737-B74B-EAF5F83DE132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -5379,7 +5379,7 @@
         <v>125</v>
       </c>
       <c r="C148" s="4">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="D148" s="3">
         <v>5</v>
@@ -5719,7 +5719,7 @@
         <v>141</v>
       </c>
       <c r="C168" s="4">
-        <v>496</v>
+        <v>187</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -6093,7 +6093,7 @@
         <v>163</v>
       </c>
       <c r="C190" s="4">
-        <v>1614</v>
+        <v>1105</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6654,7 +6654,7 @@
         <v>629</v>
       </c>
       <c r="C223" s="6">
-        <v>1806</v>
+        <v>1538</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>776</v>
@@ -8626,7 +8626,7 @@
         <v>319</v>
       </c>
       <c r="C339" s="6">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D339" s="5">
         <v>6</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05482FB6-94CB-4737-B74B-EAF5F83DE132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0B01AA-CA97-452B-8EB5-A01A4054F44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -7249,7 +7249,7 @@
         <v>225</v>
       </c>
       <c r="C258" s="4">
-        <v>997</v>
+        <v>797</v>
       </c>
       <c r="D258" s="3">
         <v>4</v>
@@ -8218,7 +8218,7 @@
         <v>721</v>
       </c>
       <c r="C315" s="6">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="D315" s="5" t="s">
         <v>776</v>
@@ -8541,7 +8541,7 @@
         <v>311</v>
       </c>
       <c r="C334" s="4">
-        <v>1685</v>
+        <v>2461</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>778</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0B01AA-CA97-452B-8EB5-A01A4054F44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5986368-B1CD-48BD-AABE-281A86ED6E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6">
-        <v>2378</v>
+        <v>1918</v>
       </c>
       <c r="D9" s="5">
         <v>3</v>
@@ -3084,7 +3084,7 @@
         <v>393</v>
       </c>
       <c r="C13" s="6">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>776</v>
@@ -3271,7 +3271,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="4">
-        <v>1546</v>
+        <v>1177</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
@@ -3339,7 +3339,7 @@
         <v>30</v>
       </c>
       <c r="C28" s="4">
-        <v>429</v>
+        <v>29</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -3373,7 +3373,7 @@
         <v>407</v>
       </c>
       <c r="C30" s="4">
-        <v>298</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>776</v>
@@ -3390,7 +3390,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="6">
-        <v>1430</v>
+        <v>1150</v>
       </c>
       <c r="D31" s="5">
         <v>3</v>
@@ -3424,7 +3424,7 @@
         <v>38</v>
       </c>
       <c r="C33" s="6">
-        <v>187</v>
+        <v>5</v>
       </c>
       <c r="D33" s="5">
         <v>2</v>
@@ -3492,7 +3492,7 @@
         <v>44</v>
       </c>
       <c r="C37" s="6">
-        <v>1614</v>
+        <v>1414</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -3526,7 +3526,7 @@
         <v>413</v>
       </c>
       <c r="C39" s="6">
-        <v>1103</v>
+        <v>607</v>
       </c>
       <c r="D39" s="5">
         <v>3</v>
@@ -3679,7 +3679,7 @@
         <v>423</v>
       </c>
       <c r="C48" s="4">
-        <v>284</v>
+        <v>4</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>776</v>
@@ -3866,7 +3866,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="6">
-        <v>1058</v>
+        <v>809</v>
       </c>
       <c r="D59" s="5">
         <v>6</v>
@@ -3917,7 +3917,7 @@
         <v>60</v>
       </c>
       <c r="C62" s="4">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="D62" s="3">
         <v>3</v>
@@ -4155,7 +4155,7 @@
         <v>461</v>
       </c>
       <c r="C76" s="4">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>776</v>
@@ -4223,7 +4223,7 @@
         <v>74</v>
       </c>
       <c r="C80" s="4">
-        <v>4337</v>
+        <v>3705</v>
       </c>
       <c r="D80" s="3">
         <v>4</v>
@@ -4325,7 +4325,7 @@
         <v>80</v>
       </c>
       <c r="C86" s="4">
-        <v>3190</v>
+        <v>2590</v>
       </c>
       <c r="D86" s="3">
         <v>3</v>
@@ -4410,7 +4410,7 @@
         <v>479</v>
       </c>
       <c r="C91" s="6">
-        <v>299</v>
+        <v>34</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>776</v>
@@ -4563,7 +4563,7 @@
         <v>86</v>
       </c>
       <c r="C100" s="4">
-        <v>1472</v>
+        <v>1096</v>
       </c>
       <c r="D100" s="3">
         <v>4</v>
@@ -4631,7 +4631,7 @@
         <v>89</v>
       </c>
       <c r="C104" s="4">
-        <v>1383</v>
+        <v>1083</v>
       </c>
       <c r="D104" s="3">
         <v>2</v>
@@ -4801,7 +4801,7 @@
         <v>511</v>
       </c>
       <c r="C114" s="4">
-        <v>781</v>
+        <v>181</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>776</v>
@@ -4818,7 +4818,7 @@
         <v>513</v>
       </c>
       <c r="C115" s="6">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>776</v>
@@ -4886,7 +4886,7 @@
         <v>99</v>
       </c>
       <c r="C119" s="6">
-        <v>956</v>
+        <v>806</v>
       </c>
       <c r="D119" s="5">
         <v>6</v>
@@ -5141,7 +5141,7 @@
         <v>533</v>
       </c>
       <c r="C134" s="4">
-        <v>792</v>
+        <v>477</v>
       </c>
       <c r="D134" s="3">
         <v>3</v>
@@ -5226,7 +5226,7 @@
         <v>115</v>
       </c>
       <c r="C139" s="6">
-        <v>825</v>
+        <v>75</v>
       </c>
       <c r="D139" s="5">
         <v>5</v>
@@ -5583,7 +5583,7 @@
         <v>133</v>
       </c>
       <c r="C160" s="4">
-        <v>1596</v>
+        <v>989</v>
       </c>
       <c r="D160" s="3">
         <v>1</v>
@@ -5702,7 +5702,7 @@
         <v>139</v>
       </c>
       <c r="C167" s="6">
-        <v>1022</v>
+        <v>722</v>
       </c>
       <c r="D167" s="5">
         <v>4</v>
@@ -5719,7 +5719,7 @@
         <v>141</v>
       </c>
       <c r="C168" s="4">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -5753,7 +5753,7 @@
         <v>577</v>
       </c>
       <c r="C170" s="4">
-        <v>1245</v>
+        <v>845</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>776</v>
@@ -5974,7 +5974,7 @@
         <v>589</v>
       </c>
       <c r="C183" s="6">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>776</v>
@@ -6076,7 +6076,7 @@
         <v>595</v>
       </c>
       <c r="C189" s="6">
-        <v>360</v>
+        <v>3</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>776</v>
@@ -6093,7 +6093,7 @@
         <v>163</v>
       </c>
       <c r="C190" s="4">
-        <v>1105</v>
+        <v>605</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6195,7 +6195,7 @@
         <v>171</v>
       </c>
       <c r="C196" s="4">
-        <v>2304</v>
+        <v>1604</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6246,7 +6246,7 @@
         <v>173</v>
       </c>
       <c r="C199" s="6">
-        <v>486</v>
+        <v>271</v>
       </c>
       <c r="D199" s="5">
         <v>3</v>
@@ -6280,7 +6280,7 @@
         <v>175</v>
       </c>
       <c r="C201" s="6">
-        <v>994</v>
+        <v>598</v>
       </c>
       <c r="D201" s="5">
         <v>5</v>
@@ -6535,7 +6535,7 @@
         <v>621</v>
       </c>
       <c r="C216" s="4">
-        <v>440</v>
+        <v>31</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>776</v>
@@ -6569,7 +6569,7 @@
         <v>191</v>
       </c>
       <c r="C218" s="4">
-        <v>869</v>
+        <v>469</v>
       </c>
       <c r="D218" s="3">
         <v>3</v>
@@ -6603,7 +6603,7 @@
         <v>195</v>
       </c>
       <c r="C220" s="4">
-        <v>607</v>
+        <v>325</v>
       </c>
       <c r="D220" s="3">
         <v>5</v>
@@ -6637,7 +6637,7 @@
         <v>627</v>
       </c>
       <c r="C222" s="4">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="D222" s="3">
         <v>4</v>
@@ -6773,7 +6773,7 @@
         <v>203</v>
       </c>
       <c r="C230" s="4">
-        <v>1560</v>
+        <v>1444</v>
       </c>
       <c r="D230" s="3">
         <v>2</v>
@@ -6909,7 +6909,7 @@
         <v>209</v>
       </c>
       <c r="C238" s="4">
-        <v>1066</v>
+        <v>619</v>
       </c>
       <c r="D238" s="3">
         <v>1</v>
@@ -7011,7 +7011,7 @@
         <v>211</v>
       </c>
       <c r="C244" s="4">
-        <v>791</v>
+        <v>491</v>
       </c>
       <c r="D244" s="3">
         <v>5</v>
@@ -7181,7 +7181,7 @@
         <v>221</v>
       </c>
       <c r="C254" s="4">
-        <v>494</v>
+        <v>414</v>
       </c>
       <c r="D254" s="3">
         <v>2</v>
@@ -7300,7 +7300,7 @@
         <v>229</v>
       </c>
       <c r="C261" s="6">
-        <v>961</v>
+        <v>639</v>
       </c>
       <c r="D261" s="5">
         <v>3</v>
@@ -7402,7 +7402,7 @@
         <v>675</v>
       </c>
       <c r="C267" s="6">
-        <v>307</v>
+        <v>2</v>
       </c>
       <c r="D267" s="5" t="s">
         <v>776</v>
@@ -7538,7 +7538,7 @@
         <v>245</v>
       </c>
       <c r="C275" s="6">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="D275" s="5">
         <v>3</v>
@@ -7572,7 +7572,7 @@
         <v>687</v>
       </c>
       <c r="C277" s="6">
-        <v>503</v>
+        <v>73</v>
       </c>
       <c r="D277" s="5" t="s">
         <v>776</v>
@@ -7606,7 +7606,7 @@
         <v>249</v>
       </c>
       <c r="C279" s="6">
-        <v>1544</v>
+        <v>1144</v>
       </c>
       <c r="D279" s="5">
         <v>2</v>
@@ -7640,7 +7640,7 @@
         <v>251</v>
       </c>
       <c r="C281" s="6">
-        <v>898</v>
+        <v>264</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -7810,7 +7810,7 @@
         <v>701</v>
       </c>
       <c r="C291" s="6">
-        <v>374</v>
+        <v>74</v>
       </c>
       <c r="D291" s="5" t="s">
         <v>776</v>
@@ -7878,7 +7878,7 @@
         <v>263</v>
       </c>
       <c r="C295" s="6">
-        <v>1096</v>
+        <v>1014</v>
       </c>
       <c r="D295" s="5">
         <v>1</v>
@@ -7997,7 +7997,7 @@
         <v>271</v>
       </c>
       <c r="C302" s="4">
-        <v>788</v>
+        <v>651</v>
       </c>
       <c r="D302" s="3">
         <v>2</v>
@@ -8082,7 +8082,7 @@
         <v>277</v>
       </c>
       <c r="C307" s="6">
-        <v>2694</v>
+        <v>2394</v>
       </c>
       <c r="D307" s="5">
         <v>5</v>
@@ -8167,7 +8167,7 @@
         <v>285</v>
       </c>
       <c r="C312" s="4">
-        <v>1521</v>
+        <v>1321</v>
       </c>
       <c r="D312" s="3">
         <v>5</v>
@@ -8252,7 +8252,7 @@
         <v>291</v>
       </c>
       <c r="C317" s="6">
-        <v>1249</v>
+        <v>938</v>
       </c>
       <c r="D317" s="5">
         <v>6</v>
@@ -8269,7 +8269,7 @@
         <v>293</v>
       </c>
       <c r="C318" s="4">
-        <v>570</v>
+        <v>355</v>
       </c>
       <c r="D318" s="3">
         <v>1</v>
@@ -8286,7 +8286,7 @@
         <v>295</v>
       </c>
       <c r="C319" s="6">
-        <v>1035</v>
+        <v>833</v>
       </c>
       <c r="D319" s="5">
         <v>5</v>
@@ -8405,7 +8405,7 @@
         <v>731</v>
       </c>
       <c r="C326" s="4">
-        <v>695</v>
+        <v>500</v>
       </c>
       <c r="D326" s="3">
         <v>4</v>
@@ -8507,7 +8507,7 @@
         <v>309</v>
       </c>
       <c r="C332" s="4">
-        <v>2063</v>
+        <v>1463</v>
       </c>
       <c r="D332" s="3">
         <v>3</v>
@@ -8728,7 +8728,7 @@
         <v>327</v>
       </c>
       <c r="C345" s="6">
-        <v>621</v>
+        <v>421</v>
       </c>
       <c r="D345" s="5">
         <v>4</v>
@@ -8762,7 +8762,7 @@
         <v>331</v>
       </c>
       <c r="C347" s="6">
-        <v>1087</v>
+        <v>200</v>
       </c>
       <c r="D347" s="5">
         <v>3</v>
@@ -9034,7 +9034,7 @@
         <v>351</v>
       </c>
       <c r="C363" s="6">
-        <v>507</v>
+        <v>312</v>
       </c>
       <c r="D363" s="5">
         <v>3</v>
@@ -9051,7 +9051,7 @@
         <v>353</v>
       </c>
       <c r="C364" s="4">
-        <v>984</v>
+        <v>236</v>
       </c>
       <c r="D364" s="3">
         <v>4</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5986368-B1CD-48BD-AABE-281A86ED6E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5951682-E2AC-4C3A-81A1-80CBA0FE6220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3220,7 +3220,7 @@
         <v>401</v>
       </c>
       <c r="C21" s="6">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D21" s="5">
         <v>2</v>
@@ -3747,7 +3747,7 @@
         <v>427</v>
       </c>
       <c r="C52" s="4">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>776</v>
@@ -4648,7 +4648,7 @@
         <v>91</v>
       </c>
       <c r="C105" s="6">
-        <v>906</v>
+        <v>621</v>
       </c>
       <c r="D105" s="5">
         <v>5</v>
@@ -5719,7 +5719,7 @@
         <v>141</v>
       </c>
       <c r="C168" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -6331,7 +6331,7 @@
         <v>181</v>
       </c>
       <c r="C204" s="4">
-        <v>6</v>
+        <v>206</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -6382,7 +6382,7 @@
         <v>611</v>
       </c>
       <c r="C207" s="6">
-        <v>1343</v>
+        <v>1107</v>
       </c>
       <c r="D207" s="5">
         <v>5</v>
@@ -6603,7 +6603,7 @@
         <v>195</v>
       </c>
       <c r="C220" s="4">
-        <v>325</v>
+        <v>95</v>
       </c>
       <c r="D220" s="3">
         <v>5</v>
@@ -7181,7 +7181,7 @@
         <v>221</v>
       </c>
       <c r="C254" s="4">
-        <v>414</v>
+        <v>614</v>
       </c>
       <c r="D254" s="3">
         <v>2</v>
@@ -7572,7 +7572,7 @@
         <v>687</v>
       </c>
       <c r="C277" s="6">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D277" s="5" t="s">
         <v>776</v>
@@ -8184,7 +8184,7 @@
         <v>719</v>
       </c>
       <c r="C313" s="6">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="D313" s="5" t="s">
         <v>776</v>
@@ -9425,7 +9425,7 @@
         <v>775</v>
       </c>
       <c r="C386" s="4">
-        <v>524</v>
+        <v>2524</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>776</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5951682-E2AC-4C3A-81A1-80CBA0FE6220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE17F256-3604-4CE0-8960-B6104096FB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -3526,7 +3526,7 @@
         <v>413</v>
       </c>
       <c r="C39" s="6">
-        <v>607</v>
+        <v>407</v>
       </c>
       <c r="D39" s="5">
         <v>3</v>
@@ -3730,7 +3730,7 @@
         <v>56</v>
       </c>
       <c r="C51" s="6">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="D51" s="5">
         <v>5</v>
@@ -4325,7 +4325,7 @@
         <v>80</v>
       </c>
       <c r="C86" s="4">
-        <v>2590</v>
+        <v>2290</v>
       </c>
       <c r="D86" s="3">
         <v>3</v>
@@ -4546,7 +4546,7 @@
         <v>493</v>
       </c>
       <c r="C99" s="6">
-        <v>652</v>
+        <v>452</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>776</v>
@@ -4631,7 +4631,7 @@
         <v>89</v>
       </c>
       <c r="C104" s="4">
-        <v>1083</v>
+        <v>873</v>
       </c>
       <c r="D104" s="3">
         <v>2</v>
@@ -4767,7 +4767,7 @@
         <v>95</v>
       </c>
       <c r="C112" s="4">
-        <v>951</v>
+        <v>751</v>
       </c>
       <c r="D112" s="3">
         <v>4</v>
@@ -4801,7 +4801,7 @@
         <v>511</v>
       </c>
       <c r="C114" s="4">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>776</v>
@@ -5634,7 +5634,7 @@
         <v>569</v>
       </c>
       <c r="C163" s="6">
-        <v>571</v>
+        <v>342</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>776</v>
@@ -5719,7 +5719,7 @@
         <v>141</v>
       </c>
       <c r="C168" s="4">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="D168" s="3">
         <v>5</v>
@@ -5787,7 +5787,7 @@
         <v>145</v>
       </c>
       <c r="C172" s="4">
-        <v>982</v>
+        <v>782</v>
       </c>
       <c r="D172" s="3">
         <v>5</v>
@@ -6093,7 +6093,7 @@
         <v>163</v>
       </c>
       <c r="C190" s="4">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="D190" s="3">
         <v>3</v>
@@ -6195,7 +6195,7 @@
         <v>171</v>
       </c>
       <c r="C196" s="4">
-        <v>1604</v>
+        <v>1404</v>
       </c>
       <c r="D196" s="3">
         <v>4</v>
@@ -6280,7 +6280,7 @@
         <v>175</v>
       </c>
       <c r="C201" s="6">
-        <v>598</v>
+        <v>398</v>
       </c>
       <c r="D201" s="5">
         <v>5</v>
@@ -6331,7 +6331,7 @@
         <v>181</v>
       </c>
       <c r="C204" s="4">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="D204" s="3">
         <v>3</v>
@@ -6569,7 +6569,7 @@
         <v>191</v>
       </c>
       <c r="C218" s="4">
-        <v>469</v>
+        <v>269</v>
       </c>
       <c r="D218" s="3">
         <v>3</v>
@@ -6909,7 +6909,7 @@
         <v>209</v>
       </c>
       <c r="C238" s="4">
-        <v>619</v>
+        <v>419</v>
       </c>
       <c r="D238" s="3">
         <v>1</v>
@@ -7300,7 +7300,7 @@
         <v>229</v>
       </c>
       <c r="C261" s="6">
-        <v>639</v>
+        <v>461</v>
       </c>
       <c r="D261" s="5">
         <v>3</v>
@@ -7640,7 +7640,7 @@
         <v>251</v>
       </c>
       <c r="C281" s="6">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -7725,7 +7725,7 @@
         <v>257</v>
       </c>
       <c r="C286" s="4">
-        <v>1411</v>
+        <v>1211</v>
       </c>
       <c r="D286" s="3">
         <v>4</v>
@@ -7810,7 +7810,7 @@
         <v>701</v>
       </c>
       <c r="C291" s="6">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D291" s="5" t="s">
         <v>776</v>
@@ -7861,7 +7861,7 @@
         <v>261</v>
       </c>
       <c r="C294" s="4">
-        <v>1009</v>
+        <v>709</v>
       </c>
       <c r="D294" s="3">
         <v>3</v>
@@ -7878,7 +7878,7 @@
         <v>263</v>
       </c>
       <c r="C295" s="6">
-        <v>1014</v>
+        <v>764</v>
       </c>
       <c r="D295" s="5">
         <v>1</v>
@@ -7997,7 +7997,7 @@
         <v>271</v>
       </c>
       <c r="C302" s="4">
-        <v>651</v>
+        <v>471</v>
       </c>
       <c r="D302" s="3">
         <v>2</v>
@@ -8167,7 +8167,7 @@
         <v>285</v>
       </c>
       <c r="C312" s="4">
-        <v>1321</v>
+        <v>1071</v>
       </c>
       <c r="D312" s="3">
         <v>5</v>
@@ -8269,7 +8269,7 @@
         <v>293</v>
       </c>
       <c r="C318" s="4">
-        <v>355</v>
+        <v>205</v>
       </c>
       <c r="D318" s="3">
         <v>1</v>
@@ -8405,7 +8405,7 @@
         <v>731</v>
       </c>
       <c r="C326" s="4">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D326" s="3">
         <v>4</v>
@@ -8541,7 +8541,7 @@
         <v>311</v>
       </c>
       <c r="C334" s="4">
-        <v>2461</v>
+        <v>2261</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>778</v>
@@ -8762,7 +8762,7 @@
         <v>331</v>
       </c>
       <c r="C347" s="6">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="D347" s="5">
         <v>3</v>
@@ -8847,7 +8847,7 @@
         <v>335</v>
       </c>
       <c r="C352" s="4">
-        <v>2996</v>
+        <v>2796</v>
       </c>
       <c r="D352" s="3">
         <v>3</v>
@@ -9051,7 +9051,7 @@
         <v>353</v>
       </c>
       <c r="C364" s="4">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="D364" s="3">
         <v>4</v>
@@ -9374,7 +9374,7 @@
         <v>375</v>
       </c>
       <c r="C383" s="6">
-        <v>454</v>
+        <v>266</v>
       </c>
       <c r="D383" s="5">
         <v>4</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\المصري\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE17F256-3604-4CE0-8960-B6104096FB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8F511A-112E-4D1F-8B1B-D776CD9CB556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9343A25C-0B88-4B0B-A742-86A483E39D84}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="797">
   <si>
     <t>اسم الزيت</t>
   </si>
@@ -2420,6 +2420,12 @@
   </si>
   <si>
     <t>0392-U</t>
+  </si>
+  <si>
+    <t>غوتشي غيلتي الكسير - رجالي</t>
+  </si>
+  <si>
+    <t>0393-M</t>
   </si>
 </sst>
 </file>
@@ -2862,7 +2868,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E394"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.26953125" bestFit="1" customWidth="1"/>
@@ -5617,7 +5623,7 @@
         <v>567</v>
       </c>
       <c r="C162" s="4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>776</v>
@@ -5634,7 +5640,7 @@
         <v>569</v>
       </c>
       <c r="C163" s="6">
-        <v>342</v>
+        <v>257</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>776</v>
@@ -6501,7 +6507,7 @@
         <v>619</v>
       </c>
       <c r="C214" s="4">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>776</v>
@@ -6722,7 +6728,7 @@
         <v>199</v>
       </c>
       <c r="C227" s="6">
-        <v>1818</v>
+        <v>1530</v>
       </c>
       <c r="D227" s="5">
         <v>1</v>
@@ -7453,7 +7459,7 @@
         <v>681</v>
       </c>
       <c r="C270" s="4">
-        <v>668</v>
+        <v>255</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>776</v>
@@ -7640,7 +7646,7 @@
         <v>251</v>
       </c>
       <c r="C281" s="6">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="D281" s="5">
         <v>6</v>
@@ -9550,6 +9556,23 @@
         <v>776</v>
       </c>
       <c r="E393" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>795</v>
+      </c>
+      <c r="B394" t="s">
+        <v>796</v>
+      </c>
+      <c r="C394">
+        <v>500</v>
+      </c>
+      <c r="D394" t="s">
+        <v>776</v>
+      </c>
+      <c r="E394" t="s">
         <v>776</v>
       </c>
     </row>
